--- a/research/traditional_assets/database/data/norway/norway_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_heathcare_information_and_technology.xlsx
@@ -1519,7 +1519,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1656,22 +1656,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09663661468084667</v>
+        <v>0.09645911412854882</v>
       </c>
       <c r="C2">
-        <v>99.57602080443476</v>
+        <v>98.73885172308928</v>
       </c>
       <c r="D2">
-        <v>94.66602080443477</v>
+        <v>94.90220830811853</v>
       </c>
       <c r="E2">
-        <v>-48.73565850292457</v>
+        <v>-47.66230191789532</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.073356585029246</v>
       </c>
       <c r="G2">
         <v>4.91</v>
@@ -1692,28 +1692,28 @@
         <v>10.61</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.05398983622697105</v>
       </c>
       <c r="N2">
-        <v>10.61</v>
+        <v>10.55601016377303</v>
       </c>
       <c r="O2">
-        <v>2.3342</v>
+        <v>2.322322236030066</v>
       </c>
       <c r="P2">
-        <v>8.2758</v>
+        <v>8.233687927742963</v>
       </c>
       <c r="Q2">
-        <v>13.7858</v>
+        <v>13.74368792774296</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09663661468084667</v>
+        <v>0.09703714558439275</v>
       </c>
       <c r="T2">
-        <v>1.174055766301309</v>
+        <v>1.183305902641865</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>196.5184697985746</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1738,22 +1738,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09645911412854882</v>
+        <v>0.09628161357625094</v>
       </c>
       <c r="C3">
-        <v>98.73885172308928</v>
+        <v>97.90286414413453</v>
       </c>
       <c r="D3">
-        <v>94.90220830811853</v>
+        <v>95.13957731419302</v>
       </c>
       <c r="E3">
-        <v>-47.66230191789532</v>
+        <v>-46.58894533286607</v>
       </c>
       <c r="F3">
-        <v>1.073356585029246</v>
+        <v>2.146713170058491</v>
       </c>
       <c r="G3">
         <v>4.91</v>
@@ -1774,28 +1774,28 @@
         <v>10.61</v>
       </c>
       <c r="M3">
-        <v>0.05398983622697105</v>
+        <v>0.1079796724539421</v>
       </c>
       <c r="N3">
-        <v>10.55601016377303</v>
+        <v>10.50202032754606</v>
       </c>
       <c r="O3">
-        <v>2.322322236030066</v>
+        <v>2.310444472060133</v>
       </c>
       <c r="P3">
-        <v>8.233687927742963</v>
+        <v>8.191575855485926</v>
       </c>
       <c r="Q3">
-        <v>13.74368792774296</v>
+        <v>13.70157585548593</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09703714558439275</v>
+        <v>0.09744585058801117</v>
       </c>
       <c r="T3">
-        <v>1.183305902641865</v>
+        <v>1.192744817275085</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>196.5184697985746</v>
+        <v>98.25923489928732</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1820,22 +1820,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09628161357625094</v>
+        <v>0.09610411302395309</v>
       </c>
       <c r="C4">
-        <v>97.90286414413453</v>
+        <v>97.0680669553068</v>
       </c>
       <c r="D4">
-        <v>95.13957731419302</v>
+        <v>95.37813671039454</v>
       </c>
       <c r="E4">
-        <v>-46.58894533286607</v>
+        <v>-45.51558874783683</v>
       </c>
       <c r="F4">
-        <v>2.146713170058491</v>
+        <v>3.220069755087737</v>
       </c>
       <c r="G4">
         <v>4.91</v>
@@ -1856,28 +1856,28 @@
         <v>10.61</v>
       </c>
       <c r="M4">
-        <v>0.1079796724539421</v>
+        <v>0.1619695086809131</v>
       </c>
       <c r="N4">
-        <v>10.50202032754606</v>
+        <v>10.44803049131909</v>
       </c>
       <c r="O4">
-        <v>2.310444472060133</v>
+        <v>2.298566708090199</v>
       </c>
       <c r="P4">
-        <v>8.191575855485926</v>
+        <v>8.149463783228889</v>
       </c>
       <c r="Q4">
-        <v>13.70157585548593</v>
+        <v>13.65946378322889</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09744585058801117</v>
+        <v>0.09786298249892071</v>
       </c>
       <c r="T4">
-        <v>1.192744817275085</v>
+        <v>1.202378348704866</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>98.25923489928732</v>
+        <v>65.50615659952489</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1902,22 +1902,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09610411302395309</v>
+        <v>0.09592661247165522</v>
       </c>
       <c r="C5">
-        <v>97.0680669553068</v>
+        <v>96.23446913370962</v>
       </c>
       <c r="D5">
-        <v>95.37813671039454</v>
+        <v>95.61789547382661</v>
       </c>
       <c r="E5">
-        <v>-45.51558874783683</v>
+        <v>-44.44223216280758</v>
       </c>
       <c r="F5">
-        <v>3.220069755087737</v>
+        <v>4.293426340116983</v>
       </c>
       <c r="G5">
         <v>4.91</v>
@@ -1938,28 +1938,28 @@
         <v>10.61</v>
       </c>
       <c r="M5">
-        <v>0.1619695086809131</v>
+        <v>0.2159593449078842</v>
       </c>
       <c r="N5">
-        <v>10.44803049131909</v>
+        <v>10.39404065509212</v>
       </c>
       <c r="O5">
-        <v>2.298566708090199</v>
+        <v>2.286688944120266</v>
       </c>
       <c r="P5">
-        <v>8.149463783228889</v>
+        <v>8.107351710971852</v>
       </c>
       <c r="Q5">
-        <v>13.65946378322889</v>
+        <v>13.61735171097185</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09786298249892071</v>
+        <v>0.09828880465797418</v>
       </c>
       <c r="T5">
-        <v>1.202378348704866</v>
+        <v>1.212212578706102</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>65.50615659952489</v>
+        <v>49.12961744964366</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1984,22 +1984,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09592661247165522</v>
+        <v>0.09574911191935737</v>
       </c>
       <c r="C6">
-        <v>96.23446913370962</v>
+        <v>95.40207974693932</v>
       </c>
       <c r="D6">
-        <v>95.61789547382661</v>
+        <v>95.85886267208555</v>
       </c>
       <c r="E6">
-        <v>-44.44223216280758</v>
+        <v>-43.36887557777834</v>
       </c>
       <c r="F6">
-        <v>4.293426340116983</v>
+        <v>5.366782925146229</v>
       </c>
       <c r="G6">
         <v>4.91</v>
@@ -2020,28 +2020,28 @@
         <v>10.61</v>
       </c>
       <c r="M6">
-        <v>0.2159593449078842</v>
+        <v>0.2699491811348553</v>
       </c>
       <c r="N6">
-        <v>10.39404065509212</v>
+        <v>10.34005081886515</v>
       </c>
       <c r="O6">
-        <v>2.286688944120266</v>
+        <v>2.274811180150332</v>
       </c>
       <c r="P6">
-        <v>8.107351710971852</v>
+        <v>8.065239638714814</v>
       </c>
       <c r="Q6">
-        <v>13.61735171097185</v>
+        <v>13.57523963871481</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09828880465797418</v>
+        <v>0.09872359149406039</v>
       </c>
       <c r="T6">
-        <v>1.212212578706102</v>
+        <v>1.222253845128416</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.12961744964366</v>
+        <v>39.30369395971493</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2066,22 +2066,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09574911191935737</v>
+        <v>0.09557161136705949</v>
       </c>
       <c r="C7">
-        <v>95.40207974693932</v>
+        <v>94.57090795422845</v>
       </c>
       <c r="D7">
-        <v>95.85886267208555</v>
+        <v>96.10104746440392</v>
       </c>
       <c r="E7">
-        <v>-43.36887557777834</v>
+        <v>-42.29551899274909</v>
       </c>
       <c r="F7">
-        <v>5.366782925146229</v>
+        <v>6.440139510175474</v>
       </c>
       <c r="G7">
         <v>4.91</v>
@@ -2102,28 +2102,28 @@
         <v>10.61</v>
       </c>
       <c r="M7">
-        <v>0.2699491811348553</v>
+        <v>0.3239390173618263</v>
       </c>
       <c r="N7">
-        <v>10.34005081886515</v>
+        <v>10.28606098263817</v>
       </c>
       <c r="O7">
-        <v>2.274811180150332</v>
+        <v>2.262933416180398</v>
       </c>
       <c r="P7">
-        <v>8.065239638714814</v>
+        <v>8.023127566457775</v>
       </c>
       <c r="Q7">
-        <v>13.57523963871481</v>
+        <v>13.53312756645778</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09872359149406039</v>
+        <v>0.09916762911389308</v>
       </c>
       <c r="T7">
-        <v>1.222253845128416</v>
+        <v>1.232508755517161</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.30369395971493</v>
+        <v>32.75307829976244</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2148,22 +2148,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09557161136705949</v>
+        <v>0.09539411081476162</v>
       </c>
       <c r="C8">
-        <v>94.57090795422845</v>
+        <v>93.74096300760615</v>
       </c>
       <c r="D8">
-        <v>96.10104746440392</v>
+        <v>96.34445910281087</v>
       </c>
       <c r="E8">
-        <v>-42.29551899274909</v>
+        <v>-41.22216240771985</v>
       </c>
       <c r="F8">
-        <v>6.440139510175474</v>
+        <v>7.513496095204719</v>
       </c>
       <c r="G8">
         <v>4.91</v>
@@ -2184,28 +2184,28 @@
         <v>10.61</v>
       </c>
       <c r="M8">
-        <v>0.3239390173618263</v>
+        <v>0.3779288535887974</v>
       </c>
       <c r="N8">
-        <v>10.28606098263817</v>
+        <v>10.2320711464112</v>
       </c>
       <c r="O8">
-        <v>2.262933416180398</v>
+        <v>2.251055652210465</v>
       </c>
       <c r="P8">
-        <v>8.023127566457775</v>
+        <v>7.98101549420074</v>
       </c>
       <c r="Q8">
-        <v>13.53312756645778</v>
+        <v>13.49101549420074</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09916762911389308</v>
+        <v>0.09962121592985121</v>
       </c>
       <c r="T8">
-        <v>1.232508755517161</v>
+        <v>1.242984201613192</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.75307829976244</v>
+        <v>28.07406711408209</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2230,22 +2230,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09539411081476165</v>
+        <v>0.09521661026246378</v>
       </c>
       <c r="C9">
-        <v>93.74096300760613</v>
+        <v>92.91225425307644</v>
       </c>
       <c r="D9">
-        <v>96.34445910281084</v>
+        <v>96.5891069333104</v>
       </c>
       <c r="E9">
-        <v>-41.22216240771984</v>
+        <v>-40.1488058226906</v>
       </c>
       <c r="F9">
-        <v>7.51349609520472</v>
+        <v>8.586852680233966</v>
       </c>
       <c r="G9">
         <v>4.91</v>
@@ -2266,28 +2266,28 @@
         <v>10.61</v>
       </c>
       <c r="M9">
-        <v>0.3779288535887974</v>
+        <v>0.4319186898157684</v>
       </c>
       <c r="N9">
-        <v>10.2320711464112</v>
+        <v>10.17808131018423</v>
       </c>
       <c r="O9">
-        <v>2.251055652210465</v>
+        <v>2.239177888240531</v>
       </c>
       <c r="P9">
-        <v>7.98101549420074</v>
+        <v>7.938903421943701</v>
       </c>
       <c r="Q9">
-        <v>13.49101549420074</v>
+        <v>13.4489034219437</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09962121592985124</v>
+        <v>0.100084663328765</v>
       </c>
       <c r="T9">
-        <v>1.242984201613193</v>
+        <v>1.253687374798268</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.07406711408209</v>
+        <v>24.56480872482183</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2312,22 +2312,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09521661026246378</v>
+        <v>0.09503910971016592</v>
       </c>
       <c r="C10">
-        <v>92.91225425307644</v>
+        <v>92.0847911318144</v>
       </c>
       <c r="D10">
-        <v>96.5891069333104</v>
+        <v>96.83500039707761</v>
       </c>
       <c r="E10">
-        <v>-40.1488058226906</v>
+        <v>-39.07544923766135</v>
       </c>
       <c r="F10">
-        <v>8.586852680233966</v>
+        <v>9.660209265263211</v>
       </c>
       <c r="G10">
         <v>4.91</v>
@@ -2348,28 +2348,28 @@
         <v>10.61</v>
       </c>
       <c r="M10">
-        <v>0.4319186898157684</v>
+        <v>0.4859085260427395</v>
       </c>
       <c r="N10">
-        <v>10.17808131018423</v>
+        <v>10.12409147395726</v>
       </c>
       <c r="O10">
-        <v>2.239177888240531</v>
+        <v>2.227300124270597</v>
       </c>
       <c r="P10">
-        <v>7.938903421943701</v>
+        <v>7.896791349686664</v>
       </c>
       <c r="Q10">
-        <v>13.4489034219437</v>
+        <v>13.40679134968666</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.100084663328765</v>
+        <v>0.1005582963847977</v>
       </c>
       <c r="T10">
-        <v>1.253687374798268</v>
+        <v>1.264625782558839</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.56480872482183</v>
+        <v>21.83538553317496</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2394,22 +2394,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09503910971016592</v>
+        <v>0.09486160915786805</v>
       </c>
       <c r="C11">
-        <v>92.0847911318144</v>
+        <v>91.25858318138062</v>
       </c>
       <c r="D11">
-        <v>96.83500039707761</v>
+        <v>97.08214903167307</v>
       </c>
       <c r="E11">
-        <v>-39.07544923766135</v>
+        <v>-38.00209265263211</v>
       </c>
       <c r="F11">
-        <v>9.660209265263211</v>
+        <v>10.73356585029246</v>
       </c>
       <c r="G11">
         <v>4.91</v>
@@ -2430,28 +2430,28 @@
         <v>10.61</v>
       </c>
       <c r="M11">
-        <v>0.4859085260427395</v>
+        <v>0.5398983622697104</v>
       </c>
       <c r="N11">
-        <v>10.12409147395726</v>
+        <v>10.07010163773029</v>
       </c>
       <c r="O11">
-        <v>2.227300124270597</v>
+        <v>2.215422360300664</v>
       </c>
       <c r="P11">
-        <v>7.896791349686664</v>
+        <v>7.854679277429627</v>
       </c>
       <c r="Q11">
-        <v>13.40679134968666</v>
+        <v>13.36467927742963</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1005582963847977</v>
+        <v>0.1010424546198534</v>
       </c>
       <c r="T11">
-        <v>1.264625782558839</v>
+        <v>1.275807266047423</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.83538553317496</v>
+        <v>19.65184697985747</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2476,22 +2476,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09486160915786805</v>
+        <v>0.09468410860557019</v>
       </c>
       <c r="C12">
-        <v>91.2585831813806</v>
+        <v>90.43364003695436</v>
       </c>
       <c r="D12">
-        <v>97.08214903167307</v>
+        <v>97.33056247227607</v>
       </c>
       <c r="E12">
-        <v>-38.00209265263211</v>
+        <v>-36.92873606760286</v>
       </c>
       <c r="F12">
-        <v>10.73356585029246</v>
+        <v>11.8069224353217</v>
       </c>
       <c r="G12">
         <v>4.91</v>
@@ -2512,28 +2512,28 @@
         <v>10.61</v>
       </c>
       <c r="M12">
-        <v>0.5398983622697106</v>
+        <v>0.5938881984966816</v>
       </c>
       <c r="N12">
-        <v>10.07010163773029</v>
+        <v>10.01611180150332</v>
       </c>
       <c r="O12">
-        <v>2.215422360300664</v>
+        <v>2.20354459633073</v>
       </c>
       <c r="P12">
-        <v>7.854679277429627</v>
+        <v>7.81256720517259</v>
       </c>
       <c r="Q12">
-        <v>13.36467927742963</v>
+        <v>13.32256720517259</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1010424546198534</v>
+        <v>0.1015374928152474</v>
       </c>
       <c r="T12">
-        <v>1.275807266047423</v>
+        <v>1.287240018827885</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.65184697985746</v>
+        <v>17.86531543623406</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2558,22 +2558,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09468410860557019</v>
+        <v>0.09450660805327232</v>
       </c>
       <c r="C13">
-        <v>90.43364003695436</v>
+        <v>89.60997143258581</v>
       </c>
       <c r="D13">
-        <v>97.33056247227607</v>
+        <v>97.58025045293675</v>
       </c>
       <c r="E13">
-        <v>-36.92873606760286</v>
+        <v>-35.85537948257362</v>
       </c>
       <c r="F13">
-        <v>11.8069224353217</v>
+        <v>12.88027902035095</v>
       </c>
       <c r="G13">
         <v>4.91</v>
@@ -2594,28 +2594,28 @@
         <v>10.61</v>
       </c>
       <c r="M13">
-        <v>0.5938881984966816</v>
+        <v>0.6478780347236526</v>
       </c>
       <c r="N13">
-        <v>10.01611180150332</v>
+        <v>9.962121965276349</v>
       </c>
       <c r="O13">
-        <v>2.20354459633073</v>
+        <v>2.191666832360797</v>
       </c>
       <c r="P13">
-        <v>7.81256720517259</v>
+        <v>7.770455132915552</v>
       </c>
       <c r="Q13">
-        <v>13.32256720517259</v>
+        <v>13.28045513291555</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1015374928152474</v>
+        <v>0.1020437818787185</v>
       </c>
       <c r="T13">
-        <v>1.287240018827885</v>
+        <v>1.298932606898812</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.86531543623406</v>
+        <v>16.37653914988122</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2640,22 +2640,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09450660805327232</v>
+        <v>0.09432910750097445</v>
       </c>
       <c r="C14">
-        <v>89.60997143258581</v>
+        <v>88.78758720246734</v>
       </c>
       <c r="D14">
-        <v>97.58025045293675</v>
+        <v>97.83122280784752</v>
       </c>
       <c r="E14">
-        <v>-35.85537948257362</v>
+        <v>-34.78202289754437</v>
       </c>
       <c r="F14">
-        <v>12.88027902035095</v>
+        <v>13.95363560538019</v>
       </c>
       <c r="G14">
         <v>4.91</v>
@@ -2676,28 +2676,28 @@
         <v>10.61</v>
       </c>
       <c r="M14">
-        <v>0.6478780347236526</v>
+        <v>0.7018678709506236</v>
       </c>
       <c r="N14">
-        <v>9.962121965276349</v>
+        <v>9.908132129049378</v>
       </c>
       <c r="O14">
-        <v>2.191666832360797</v>
+        <v>2.179789068390863</v>
       </c>
       <c r="P14">
-        <v>7.770455132915552</v>
+        <v>7.728343060658514</v>
       </c>
       <c r="Q14">
-        <v>13.28045513291555</v>
+        <v>13.23834306065852</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1020437818787185</v>
+        <v>0.102561709771235</v>
       </c>
       <c r="T14">
-        <v>1.298932606898812</v>
+        <v>1.310893990097806</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.37653914988122</v>
+        <v>15.11680536912113</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2722,22 +2722,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09432910750097445</v>
+        <v>0.09415160694867659</v>
       </c>
       <c r="C15">
-        <v>88.78758720246734</v>
+        <v>87.96649728222475</v>
       </c>
       <c r="D15">
-        <v>97.83122280784752</v>
+        <v>98.0834894726342</v>
       </c>
       <c r="E15">
-        <v>-34.78202289754437</v>
+        <v>-33.70866631251513</v>
       </c>
       <c r="F15">
-        <v>13.95363560538019</v>
+        <v>15.02699219040944</v>
       </c>
       <c r="G15">
         <v>4.91</v>
@@ -2758,28 +2758,28 @@
         <v>10.61</v>
       </c>
       <c r="M15">
-        <v>0.7018678709506236</v>
+        <v>0.7558577071775947</v>
       </c>
       <c r="N15">
-        <v>9.908132129049378</v>
+        <v>9.854142292822406</v>
       </c>
       <c r="O15">
-        <v>2.179789068390863</v>
+        <v>2.167911304420929</v>
       </c>
       <c r="P15">
-        <v>7.728343060658514</v>
+        <v>7.686230988401476</v>
       </c>
       <c r="Q15">
-        <v>13.23834306065852</v>
+        <v>13.19623098840148</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.102561709771235</v>
+        <v>0.1030916824984612</v>
       </c>
       <c r="T15">
-        <v>1.310893990097806</v>
+        <v>1.323133544999103</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.11680536912113</v>
+        <v>14.03703355704105</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2804,22 +2804,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09415160694867659</v>
+        <v>0.09397410639637874</v>
       </c>
       <c r="C16">
-        <v>87.96649728222475</v>
+        <v>87.14671171022853</v>
       </c>
       <c r="D16">
-        <v>98.0834894726342</v>
+        <v>98.33706048566722</v>
       </c>
       <c r="E16">
-        <v>-33.70866631251513</v>
+        <v>-32.63530972748588</v>
       </c>
       <c r="F16">
-        <v>15.02699219040944</v>
+        <v>16.10034877543869</v>
       </c>
       <c r="G16">
         <v>4.91</v>
@@ -2840,28 +2840,28 @@
         <v>10.61</v>
       </c>
       <c r="M16">
-        <v>0.7558577071775947</v>
+        <v>0.8098475434045659</v>
       </c>
       <c r="N16">
-        <v>9.854142292822406</v>
+        <v>9.800152456595436</v>
       </c>
       <c r="O16">
-        <v>2.167911304420929</v>
+        <v>2.156033540450996</v>
       </c>
       <c r="P16">
-        <v>7.686230988401476</v>
+        <v>7.64411891614444</v>
       </c>
       <c r="Q16">
-        <v>13.19623098840148</v>
+        <v>13.15411891614444</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1030916824984612</v>
+        <v>0.1036341251722103</v>
       </c>
       <c r="T16">
-        <v>1.323133544999103</v>
+        <v>1.335661089427489</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.03703355704105</v>
+        <v>13.10123131990497</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2886,22 +2886,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09397410639637874</v>
+        <v>0.09398380584408086</v>
       </c>
       <c r="C17">
-        <v>87.14671171022854</v>
+        <v>86.05946497736282</v>
       </c>
       <c r="D17">
-        <v>98.33706048566722</v>
+        <v>98.32317033783076</v>
       </c>
       <c r="E17">
-        <v>-32.63530972748588</v>
+        <v>-31.56195314245663</v>
       </c>
       <c r="F17">
-        <v>16.10034877543868</v>
+        <v>17.17370536046793</v>
       </c>
       <c r="G17">
         <v>4.91</v>
@@ -2922,45 +2922,45 @@
         <v>10.61</v>
       </c>
       <c r="M17">
-        <v>0.8098475434045657</v>
+        <v>0.8895979376722388</v>
       </c>
       <c r="N17">
-        <v>9.800152456595436</v>
+        <v>9.720402062327762</v>
       </c>
       <c r="O17">
-        <v>2.156033540450996</v>
+        <v>2.138488453712108</v>
       </c>
       <c r="P17">
-        <v>7.64411891614444</v>
+        <v>7.581913608615655</v>
       </c>
       <c r="Q17">
-        <v>13.15411891614444</v>
+        <v>13.09191360861566</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1036341251722103</v>
+        <v>0.1041894831477153</v>
       </c>
       <c r="T17">
-        <v>1.335661089427489</v>
+        <v>1.348486908723218</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.10123131990498</v>
+        <v>11.92673628241832</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2968,22 +2968,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09398380584408086</v>
+        <v>0.09381800529178301</v>
       </c>
       <c r="C18">
-        <v>86.05946497736282</v>
+        <v>85.22408505075155</v>
       </c>
       <c r="D18">
-        <v>98.32317033783076</v>
+        <v>98.56114699624874</v>
       </c>
       <c r="E18">
-        <v>-31.56195314245663</v>
+        <v>-30.48859655742739</v>
       </c>
       <c r="F18">
-        <v>17.17370536046793</v>
+        <v>18.24706194549718</v>
       </c>
       <c r="G18">
         <v>4.91</v>
@@ -3004,28 +3004,28 @@
         <v>10.61</v>
       </c>
       <c r="M18">
-        <v>0.8895979376722388</v>
+        <v>0.9451978087767537</v>
       </c>
       <c r="N18">
-        <v>9.720402062327762</v>
+        <v>9.664802191223247</v>
       </c>
       <c r="O18">
-        <v>2.138488453712108</v>
+        <v>2.126256482069115</v>
       </c>
       <c r="P18">
-        <v>7.581913608615655</v>
+        <v>7.538545709154132</v>
       </c>
       <c r="Q18">
-        <v>13.09191360861566</v>
+        <v>13.04854570915413</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1041894831477153</v>
+        <v>0.1047582232431121</v>
       </c>
       <c r="T18">
-        <v>1.348486908723218</v>
+        <v>1.361621783905591</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.92673628241832</v>
+        <v>11.22516355992312</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3050,22 +3050,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09381800529178301</v>
+        <v>0.09365220473948514</v>
       </c>
       <c r="C19">
-        <v>85.22408505075155</v>
+        <v>84.38985989353677</v>
       </c>
       <c r="D19">
-        <v>98.56114699624874</v>
+        <v>98.80027842406319</v>
       </c>
       <c r="E19">
-        <v>-30.48859655742739</v>
+        <v>-29.41523997239814</v>
       </c>
       <c r="F19">
-        <v>18.24706194549718</v>
+        <v>19.32041853052642</v>
       </c>
       <c r="G19">
         <v>4.91</v>
@@ -3086,28 +3086,28 @@
         <v>10.61</v>
       </c>
       <c r="M19">
-        <v>0.9451978087767537</v>
+        <v>1.000797679881269</v>
       </c>
       <c r="N19">
-        <v>9.664802191223247</v>
+        <v>9.609202320118733</v>
       </c>
       <c r="O19">
-        <v>2.126256482069115</v>
+        <v>2.114024510426121</v>
       </c>
       <c r="P19">
-        <v>7.538545709154132</v>
+        <v>7.495177809692612</v>
       </c>
       <c r="Q19">
-        <v>13.04854570915413</v>
+        <v>13.00517780969261</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1047582232431121</v>
+        <v>0.1053408350481526</v>
       </c>
       <c r="T19">
-        <v>1.361621783905591</v>
+        <v>1.37507702189729</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.22516355992312</v>
+        <v>10.60154336214962</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3132,22 +3132,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09365220473948514</v>
+        <v>0.09348640418718729</v>
       </c>
       <c r="C20">
-        <v>84.38985989353677</v>
+        <v>83.55679793134877</v>
       </c>
       <c r="D20">
-        <v>98.80027842406319</v>
+        <v>99.04057304690444</v>
       </c>
       <c r="E20">
-        <v>-29.41523997239814</v>
+        <v>-28.3418833873689</v>
       </c>
       <c r="F20">
-        <v>19.32041853052642</v>
+        <v>20.39377511555567</v>
       </c>
       <c r="G20">
         <v>4.91</v>
@@ -3168,28 +3168,28 @@
         <v>10.61</v>
       </c>
       <c r="M20">
-        <v>1.000797679881269</v>
+        <v>1.056397550985783</v>
       </c>
       <c r="N20">
-        <v>9.609202320118733</v>
+        <v>9.553602449014218</v>
       </c>
       <c r="O20">
-        <v>2.114024510426121</v>
+        <v>2.101792538783128</v>
       </c>
       <c r="P20">
-        <v>7.495177809692612</v>
+        <v>7.45180991023109</v>
       </c>
       <c r="Q20">
-        <v>13.00517780969261</v>
+        <v>12.96180991023109</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1053408350481526</v>
+        <v>0.1059378323298608</v>
       </c>
       <c r="T20">
-        <v>1.375077021897289</v>
+        <v>1.388864487987549</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.60154336214962</v>
+        <v>10.04356739572069</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3214,22 +3214,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09348640418718729</v>
+        <v>0.09358580363488943</v>
       </c>
       <c r="C21">
-        <v>83.55679793134877</v>
+        <v>82.33924168231617</v>
       </c>
       <c r="D21">
-        <v>99.04057304690444</v>
+        <v>98.89637338290109</v>
       </c>
       <c r="E21">
-        <v>-28.3418833873689</v>
+        <v>-27.26852680233965</v>
       </c>
       <c r="F21">
-        <v>20.39377511555567</v>
+        <v>21.46713170058491</v>
       </c>
       <c r="G21">
         <v>4.91</v>
@@ -3250,45 +3250,45 @@
         <v>10.61</v>
       </c>
       <c r="M21">
-        <v>1.056397550985783</v>
+        <v>1.148491545981293</v>
       </c>
       <c r="N21">
-        <v>9.553602449014218</v>
+        <v>9.461508454018709</v>
       </c>
       <c r="O21">
-        <v>2.101792538783128</v>
+        <v>2.081531859884116</v>
       </c>
       <c r="P21">
-        <v>7.45180991023109</v>
+        <v>7.379976594134593</v>
       </c>
       <c r="Q21">
-        <v>12.96180991023109</v>
+        <v>12.88997659413459</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1059378323298608</v>
+        <v>0.1065497545436118</v>
       </c>
       <c r="T21">
-        <v>1.388864487987549</v>
+        <v>1.402996640730064</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.04356739572069</v>
+        <v>9.238204701746078</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3296,22 +3296,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09358580363488943</v>
+        <v>0.09343326308259157</v>
       </c>
       <c r="C22">
-        <v>82.33924168231617</v>
+        <v>81.48734967233418</v>
       </c>
       <c r="D22">
-        <v>98.89637338290109</v>
+        <v>99.11783795794834</v>
       </c>
       <c r="E22">
-        <v>-27.26852680233965</v>
+        <v>-26.19517021731041</v>
       </c>
       <c r="F22">
-        <v>21.46713170058491</v>
+        <v>22.54048828561416</v>
       </c>
       <c r="G22">
         <v>4.91</v>
@@ -3332,28 +3332,28 @@
         <v>10.61</v>
       </c>
       <c r="M22">
-        <v>1.148491545981293</v>
+        <v>1.205916123280357</v>
       </c>
       <c r="N22">
-        <v>9.461508454018709</v>
+        <v>9.404083876719644</v>
       </c>
       <c r="O22">
-        <v>2.081531859884116</v>
+        <v>2.068898452878322</v>
       </c>
       <c r="P22">
-        <v>7.379976594134593</v>
+        <v>7.335185423841322</v>
       </c>
       <c r="Q22">
-        <v>12.88997659413459</v>
+        <v>12.84518542384132</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1065497545436118</v>
+        <v>0.1071771684589767</v>
       </c>
       <c r="T22">
-        <v>1.402996640730064</v>
+        <v>1.417486569491378</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.238204701746078</v>
+        <v>8.798290192139122</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3378,22 +3378,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09343326308259156</v>
+        <v>0.09328072253029369</v>
       </c>
       <c r="C23">
-        <v>81.4873496723342</v>
+        <v>80.63645176629606</v>
       </c>
       <c r="D23">
-        <v>99.11783795794837</v>
+        <v>99.34029663693947</v>
       </c>
       <c r="E23">
-        <v>-26.19517021731041</v>
+        <v>-25.12181363228116</v>
       </c>
       <c r="F23">
-        <v>22.54048828561416</v>
+        <v>23.6138448706434</v>
       </c>
       <c r="G23">
         <v>4.91</v>
@@ -3414,28 +3414,28 @@
         <v>10.61</v>
       </c>
       <c r="M23">
-        <v>1.205916123280357</v>
+        <v>1.263340700579422</v>
       </c>
       <c r="N23">
-        <v>9.404083876719644</v>
+        <v>9.34665929942058</v>
       </c>
       <c r="O23">
-        <v>2.068898452878322</v>
+        <v>2.056265045872527</v>
       </c>
       <c r="P23">
-        <v>7.335185423841322</v>
+        <v>7.290394253548053</v>
       </c>
       <c r="Q23">
-        <v>12.84518542384132</v>
+        <v>12.80039425354805</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1071771684589767</v>
+        <v>0.1078206699106329</v>
       </c>
       <c r="T23">
-        <v>1.417486569491378</v>
+        <v>1.432348034887597</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.798290192139124</v>
+        <v>8.398367910678253</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3460,22 +3460,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09328072253029369</v>
+        <v>0.09312818197799584</v>
       </c>
       <c r="C24">
-        <v>80.63645176629606</v>
+        <v>79.78655467271686</v>
       </c>
       <c r="D24">
-        <v>99.34029663693947</v>
+        <v>99.56375612838951</v>
       </c>
       <c r="E24">
-        <v>-25.12181363228116</v>
+        <v>-24.04845704725192</v>
       </c>
       <c r="F24">
-        <v>23.6138448706434</v>
+        <v>24.68720145567265</v>
       </c>
       <c r="G24">
         <v>4.91</v>
@@ -3496,28 +3496,28 @@
         <v>10.61</v>
       </c>
       <c r="M24">
-        <v>1.263340700579422</v>
+        <v>1.320765277878487</v>
       </c>
       <c r="N24">
-        <v>9.34665929942058</v>
+        <v>9.289234722121515</v>
       </c>
       <c r="O24">
-        <v>2.056265045872527</v>
+        <v>2.043631638866733</v>
       </c>
       <c r="P24">
-        <v>7.290394253548053</v>
+        <v>7.245603083254782</v>
       </c>
       <c r="Q24">
-        <v>12.80039425354805</v>
+        <v>12.75560308325478</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1078206699106329</v>
+        <v>0.1084808856857089</v>
       </c>
       <c r="T24">
-        <v>1.432348034887597</v>
+        <v>1.44759551237203</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.398367910678253</v>
+        <v>8.033221479779201</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3542,22 +3542,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09312818197799584</v>
+        <v>0.09297564142569799</v>
       </c>
       <c r="C25">
-        <v>79.78655467271686</v>
+        <v>78.93766516060934</v>
       </c>
       <c r="D25">
-        <v>99.56375612838951</v>
+        <v>99.78822320131124</v>
       </c>
       <c r="E25">
-        <v>-24.04845704725192</v>
+        <v>-22.97510046222267</v>
       </c>
       <c r="F25">
-        <v>24.68720145567265</v>
+        <v>25.76055804070189</v>
       </c>
       <c r="G25">
         <v>4.91</v>
@@ -3578,28 +3578,28 @@
         <v>10.61</v>
       </c>
       <c r="M25">
-        <v>1.320765277878487</v>
+        <v>1.378189855177551</v>
       </c>
       <c r="N25">
-        <v>9.289234722121515</v>
+        <v>9.23181014482245</v>
       </c>
       <c r="O25">
-        <v>2.043631638866733</v>
+        <v>2.030998231860939</v>
       </c>
       <c r="P25">
-        <v>7.245603083254782</v>
+        <v>7.200811912961511</v>
       </c>
       <c r="Q25">
-        <v>12.75560308325478</v>
+        <v>12.71081191296151</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1084808856857089</v>
+        <v>0.1091584755601289</v>
       </c>
       <c r="T25">
-        <v>1.44759551237203</v>
+        <v>1.463244239263948</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.033221479779201</v>
+        <v>7.698503918121732</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3624,22 +3624,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09297564142569799</v>
+        <v>0.09297910087340011</v>
       </c>
       <c r="C26">
-        <v>78.93766516060934</v>
+        <v>77.85920669943776</v>
       </c>
       <c r="D26">
-        <v>99.78822320131124</v>
+        <v>99.78312132516891</v>
       </c>
       <c r="E26">
-        <v>-22.97510046222267</v>
+        <v>-21.90174387719343</v>
       </c>
       <c r="F26">
-        <v>25.76055804070189</v>
+        <v>26.83391462573114</v>
       </c>
       <c r="G26">
         <v>4.91</v>
@@ -3660,45 +3660,45 @@
         <v>10.61</v>
       </c>
       <c r="M26">
-        <v>1.378189855177551</v>
+        <v>1.457081564177201</v>
       </c>
       <c r="N26">
-        <v>9.23181014482245</v>
+        <v>9.1529184358228</v>
       </c>
       <c r="O26">
-        <v>2.030998231860939</v>
+        <v>2.013642055881016</v>
       </c>
       <c r="P26">
-        <v>7.200811912961511</v>
+        <v>7.139276379941784</v>
       </c>
       <c r="Q26">
-        <v>12.71081191296151</v>
+        <v>12.64927637994178</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1091584755601289</v>
+        <v>0.1098541344978668</v>
       </c>
       <c r="T26">
-        <v>1.463244239263948</v>
+        <v>1.47931026553965</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.698503918121732</v>
+        <v>7.28167884410188</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3706,22 +3706,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09297910087340011</v>
+        <v>0.09283280032110226</v>
       </c>
       <c r="C27">
-        <v>77.85920669943776</v>
+        <v>77.00206567073211</v>
       </c>
       <c r="D27">
-        <v>99.78312132516891</v>
+        <v>99.9993368814925</v>
       </c>
       <c r="E27">
-        <v>-21.90174387719343</v>
+        <v>-20.82838729216418</v>
       </c>
       <c r="F27">
-        <v>26.83391462573114</v>
+        <v>27.90727121076038</v>
       </c>
       <c r="G27">
         <v>4.91</v>
@@ -3742,28 +3742,28 @@
         <v>10.61</v>
       </c>
       <c r="M27">
-        <v>1.457081564177201</v>
+        <v>1.515364826744289</v>
       </c>
       <c r="N27">
-        <v>9.1529184358228</v>
+        <v>9.094635173255712</v>
       </c>
       <c r="O27">
-        <v>2.013642055881016</v>
+        <v>2.000819738116257</v>
       </c>
       <c r="P27">
-        <v>7.139276379941784</v>
+        <v>7.093815435139455</v>
       </c>
       <c r="Q27">
-        <v>12.64927637994178</v>
+        <v>12.60381543513946</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1098541344978668</v>
+        <v>0.1105685950285166</v>
       </c>
       <c r="T27">
-        <v>1.47931026553965</v>
+        <v>1.495810508741722</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.28167884410188</v>
+        <v>7.001614273174885</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3788,22 +3788,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09283280032110226</v>
+        <v>0.09268649976880437</v>
       </c>
       <c r="C28">
-        <v>77.00206567073211</v>
+        <v>76.14586369233517</v>
       </c>
       <c r="D28">
-        <v>99.9993368814925</v>
+        <v>100.2164914881248</v>
       </c>
       <c r="E28">
-        <v>-20.82838729216418</v>
+        <v>-19.75503070713493</v>
       </c>
       <c r="F28">
-        <v>27.90727121076038</v>
+        <v>28.98062779578963</v>
       </c>
       <c r="G28">
         <v>4.91</v>
@@ -3824,28 +3824,28 @@
         <v>10.61</v>
       </c>
       <c r="M28">
-        <v>1.515364826744289</v>
+        <v>1.573648089311377</v>
       </c>
       <c r="N28">
-        <v>9.094635173255712</v>
+        <v>9.036351910688625</v>
       </c>
       <c r="O28">
-        <v>2.000819738116257</v>
+        <v>1.987997420351497</v>
       </c>
       <c r="P28">
-        <v>7.093815435139455</v>
+        <v>7.048354490337127</v>
       </c>
       <c r="Q28">
-        <v>12.60381543513946</v>
+        <v>12.55835449033713</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1105685950285166</v>
+        <v>0.11130262982028</v>
       </c>
       <c r="T28">
-        <v>1.495810508741722</v>
+        <v>1.512762813401386</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.001614273174885</v>
+        <v>6.74229522602026</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3870,22 +3870,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09268649976880437</v>
+        <v>0.09254019921650654</v>
       </c>
       <c r="C29">
-        <v>76.14586369233517</v>
+        <v>75.29060689517405</v>
       </c>
       <c r="D29">
-        <v>100.2164914881248</v>
+        <v>100.4345912759929</v>
       </c>
       <c r="E29">
-        <v>-19.75503070713493</v>
+        <v>-18.68167412210569</v>
       </c>
       <c r="F29">
-        <v>28.98062779578963</v>
+        <v>30.05398438081888</v>
       </c>
       <c r="G29">
         <v>4.91</v>
@@ -3906,28 +3906,28 @@
         <v>10.61</v>
       </c>
       <c r="M29">
-        <v>1.573648089311377</v>
+        <v>1.631931351878465</v>
       </c>
       <c r="N29">
-        <v>9.036351910688625</v>
+        <v>8.978068648121535</v>
       </c>
       <c r="O29">
-        <v>1.987997420351497</v>
+        <v>1.975175102586738</v>
       </c>
       <c r="P29">
-        <v>7.048354490337127</v>
+        <v>7.002893545534798</v>
       </c>
       <c r="Q29">
-        <v>12.55835449033713</v>
+        <v>12.5128935455348</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.11130262982028</v>
+        <v>0.1120570544673702</v>
       </c>
       <c r="T29">
-        <v>1.512762813401386</v>
+        <v>1.530186015412706</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.74229522602026</v>
+        <v>6.501498967948107</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3952,22 +3952,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09254019921650654</v>
+        <v>0.09239389866420865</v>
       </c>
       <c r="C30">
-        <v>75.29060689517405</v>
+        <v>74.43630146366317</v>
       </c>
       <c r="D30">
-        <v>100.4345912759929</v>
+        <v>100.6536424295113</v>
       </c>
       <c r="E30">
-        <v>-18.68167412210569</v>
+        <v>-17.60831753707644</v>
       </c>
       <c r="F30">
-        <v>30.05398438081888</v>
+        <v>31.12734096584813</v>
       </c>
       <c r="G30">
         <v>4.91</v>
@@ -3988,28 +3988,28 @@
         <v>10.61</v>
       </c>
       <c r="M30">
-        <v>1.631931351878465</v>
+        <v>1.690214614445553</v>
       </c>
       <c r="N30">
-        <v>8.978068648121535</v>
+        <v>8.919785385554448</v>
       </c>
       <c r="O30">
-        <v>1.975175102586738</v>
+        <v>1.962352784821979</v>
       </c>
       <c r="P30">
-        <v>7.002893545534798</v>
+        <v>6.957432600732469</v>
       </c>
       <c r="Q30">
-        <v>12.5128935455348</v>
+        <v>12.46743260073247</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1120570544673702</v>
+        <v>0.1128327305129699</v>
       </c>
       <c r="T30">
-        <v>1.530186015412706</v>
+        <v>1.548100011846881</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.501498967948107</v>
+        <v>6.27730934836369</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4034,22 +4034,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09239389866420865</v>
+        <v>0.0924815981119108</v>
       </c>
       <c r="C31">
-        <v>74.43630146366317</v>
+        <v>73.23152072630823</v>
       </c>
       <c r="D31">
-        <v>100.6536424295113</v>
+        <v>100.5222182771856</v>
       </c>
       <c r="E31">
-        <v>-17.60831753707645</v>
+        <v>-16.5349609520472</v>
       </c>
       <c r="F31">
-        <v>31.12734096584812</v>
+        <v>32.20069755087736</v>
       </c>
       <c r="G31">
         <v>4.91</v>
@@ -4070,45 +4070,45 @@
         <v>10.61</v>
       </c>
       <c r="M31">
-        <v>1.690214614445553</v>
+        <v>1.780698574563518</v>
       </c>
       <c r="N31">
-        <v>8.919785385554448</v>
+        <v>8.829301425436483</v>
       </c>
       <c r="O31">
-        <v>1.962352784821979</v>
+        <v>1.942446313596026</v>
       </c>
       <c r="P31">
-        <v>6.957432600732469</v>
+        <v>6.886855111840458</v>
       </c>
       <c r="Q31">
-        <v>12.46743260073247</v>
+        <v>12.39685511184046</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1128327305129699</v>
+        <v>0.1136305687313011</v>
       </c>
       <c r="T31">
-        <v>1.548100011846881</v>
+        <v>1.566525836750604</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.277309348363691</v>
+        <v>5.958335763030925</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4116,22 +4116,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0924815981119108</v>
+        <v>0.09234309755961294</v>
       </c>
       <c r="C32">
-        <v>73.23152072630823</v>
+        <v>72.365874838485</v>
       </c>
       <c r="D32">
-        <v>100.5222182771856</v>
+        <v>100.7299289743916</v>
       </c>
       <c r="E32">
-        <v>-16.5349609520472</v>
+        <v>-15.46160436701796</v>
       </c>
       <c r="F32">
-        <v>32.20069755087736</v>
+        <v>33.27405413590661</v>
       </c>
       <c r="G32">
         <v>4.91</v>
@@ -4152,28 +4152,28 @@
         <v>10.61</v>
       </c>
       <c r="M32">
-        <v>1.780698574563518</v>
+        <v>1.840055193715636</v>
       </c>
       <c r="N32">
-        <v>8.829301425436483</v>
+        <v>8.769944806284366</v>
       </c>
       <c r="O32">
-        <v>1.942446313596026</v>
+        <v>1.92938785738256</v>
       </c>
       <c r="P32">
-        <v>6.886855111840458</v>
+        <v>6.840556948901805</v>
       </c>
       <c r="Q32">
-        <v>12.39685511184046</v>
+        <v>12.3505569489018</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1136305687313011</v>
+        <v>0.1144515326950912</v>
       </c>
       <c r="T32">
-        <v>1.566525836750604</v>
+        <v>1.585485743535594</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.958335763030925</v>
+        <v>5.766131383578315</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4198,22 +4198,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09234309755961294</v>
+        <v>0.09220459700731506</v>
       </c>
       <c r="C33">
-        <v>72.365874838485</v>
+        <v>71.50108912003853</v>
       </c>
       <c r="D33">
-        <v>100.7299289743916</v>
+        <v>100.9384998409744</v>
       </c>
       <c r="E33">
-        <v>-15.46160436701796</v>
+        <v>-14.3882477819887</v>
       </c>
       <c r="F33">
-        <v>33.27405413590661</v>
+        <v>34.34741072093586</v>
       </c>
       <c r="G33">
         <v>4.91</v>
@@ -4234,28 +4234,28 @@
         <v>10.61</v>
       </c>
       <c r="M33">
-        <v>1.840055193715636</v>
+        <v>1.899411812867753</v>
       </c>
       <c r="N33">
-        <v>8.769944806284366</v>
+        <v>8.710588187132249</v>
       </c>
       <c r="O33">
-        <v>1.92938785738256</v>
+        <v>1.916329401169095</v>
       </c>
       <c r="P33">
-        <v>6.840556948901805</v>
+        <v>6.794258785963154</v>
       </c>
       <c r="Q33">
-        <v>12.3505569489018</v>
+        <v>12.30425878596315</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1144515326950912</v>
+        <v>0.1152966426578163</v>
       </c>
       <c r="T33">
-        <v>1.585485743535594</v>
+        <v>1.60500329463779</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.766131383578315</v>
+        <v>5.585939777841491</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4280,22 +4280,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09220459700731506</v>
+        <v>0.0920660964550172</v>
       </c>
       <c r="C34">
-        <v>71.50108912003853</v>
+        <v>70.63716892524209</v>
       </c>
       <c r="D34">
-        <v>100.9384998409744</v>
+        <v>101.1479362312072</v>
       </c>
       <c r="E34">
-        <v>-14.3882477819887</v>
+        <v>-13.31489119695946</v>
       </c>
       <c r="F34">
-        <v>34.34741072093586</v>
+        <v>35.42076730596511</v>
       </c>
       <c r="G34">
         <v>4.91</v>
@@ -4316,28 +4316,28 @@
         <v>10.61</v>
       </c>
       <c r="M34">
-        <v>1.899411812867753</v>
+        <v>1.95876843201987</v>
       </c>
       <c r="N34">
-        <v>8.710588187132249</v>
+        <v>8.651231567980131</v>
       </c>
       <c r="O34">
-        <v>1.916329401169095</v>
+        <v>1.903270944955629</v>
       </c>
       <c r="P34">
-        <v>6.794258785963154</v>
+        <v>6.747960623024502</v>
       </c>
       <c r="Q34">
-        <v>12.30425878596315</v>
+        <v>12.2579606230245</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1152966426578163</v>
+        <v>0.1161669797836078</v>
       </c>
       <c r="T34">
-        <v>1.60500329463779</v>
+        <v>1.625103459205723</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.585939777841491</v>
+        <v>5.416668875482658</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4362,22 +4362,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0920660964550172</v>
+        <v>0.09192759590271934</v>
       </c>
       <c r="C35">
-        <v>70.63716892524209</v>
+        <v>69.77411965289943</v>
       </c>
       <c r="D35">
-        <v>101.1479362312072</v>
+        <v>101.3582435438938</v>
       </c>
       <c r="E35">
-        <v>-13.31489119695946</v>
+        <v>-12.24153461193021</v>
       </c>
       <c r="F35">
-        <v>35.42076730596511</v>
+        <v>36.49412389099435</v>
       </c>
       <c r="G35">
         <v>4.91</v>
@@ -4398,28 +4398,28 @@
         <v>10.61</v>
       </c>
       <c r="M35">
-        <v>1.95876843201987</v>
+        <v>2.018125051171988</v>
       </c>
       <c r="N35">
-        <v>8.651231567980131</v>
+        <v>8.591874948828014</v>
       </c>
       <c r="O35">
-        <v>1.903270944955629</v>
+        <v>1.890212488742163</v>
       </c>
       <c r="P35">
-        <v>6.747960623024502</v>
+        <v>6.701662460085851</v>
       </c>
       <c r="Q35">
-        <v>12.2579606230245</v>
+        <v>12.21166246008585</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1161669797836078</v>
+        <v>0.117063690761696</v>
       </c>
       <c r="T35">
-        <v>1.625103459205723</v>
+        <v>1.645812719669653</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.416668875482658</v>
+        <v>5.257355085027286</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4444,22 +4444,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09192759590271934</v>
+        <v>0.09178909535042148</v>
       </c>
       <c r="C36">
-        <v>69.77411965289943</v>
+        <v>68.91194674680875</v>
       </c>
       <c r="D36">
-        <v>101.3582435438938</v>
+        <v>101.5694272228323</v>
       </c>
       <c r="E36">
-        <v>-12.24153461193021</v>
+        <v>-11.16817802690097</v>
       </c>
       <c r="F36">
-        <v>36.49412389099435</v>
+        <v>37.5674804760236</v>
       </c>
       <c r="G36">
         <v>4.91</v>
@@ -4480,28 +4480,28 @@
         <v>10.61</v>
       </c>
       <c r="M36">
-        <v>2.018125051171988</v>
+        <v>2.077481670324105</v>
       </c>
       <c r="N36">
-        <v>8.591874948828014</v>
+        <v>8.532518329675897</v>
       </c>
       <c r="O36">
-        <v>1.890212488742163</v>
+        <v>1.877154032528697</v>
       </c>
       <c r="P36">
-        <v>6.701662460085851</v>
+        <v>6.6553642971472</v>
       </c>
       <c r="Q36">
-        <v>12.21166246008585</v>
+        <v>12.1653642971472</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.117063690761696</v>
+        <v>0.1179879928468023</v>
       </c>
       <c r="T36">
-        <v>1.645812719669653</v>
+        <v>1.667159188147859</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.257355085027286</v>
+        <v>5.107144939740793</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4526,22 +4526,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09178909535042148</v>
+        <v>0.09165059479812361</v>
       </c>
       <c r="C37">
-        <v>68.91194674680875</v>
+        <v>68.05065569623241</v>
       </c>
       <c r="D37">
-        <v>101.5694272228323</v>
+        <v>101.7814927572853</v>
       </c>
       <c r="E37">
-        <v>-11.16817802690097</v>
+        <v>-10.09482144187172</v>
       </c>
       <c r="F37">
-        <v>37.5674804760236</v>
+        <v>38.64083706105285</v>
       </c>
       <c r="G37">
         <v>4.91</v>
@@ -4562,28 +4562,28 @@
         <v>10.61</v>
       </c>
       <c r="M37">
-        <v>2.077481670324105</v>
+        <v>2.136838289476223</v>
       </c>
       <c r="N37">
-        <v>8.532518329675897</v>
+        <v>8.47316171052378</v>
       </c>
       <c r="O37">
-        <v>1.877154032528697</v>
+        <v>1.864095576315232</v>
       </c>
       <c r="P37">
-        <v>6.6553642971472</v>
+        <v>6.609066134208548</v>
       </c>
       <c r="Q37">
-        <v>12.1653642971472</v>
+        <v>12.11906613420855</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1179879928468023</v>
+        <v>0.1189411793720682</v>
       </c>
       <c r="T37">
-        <v>1.667159188147859</v>
+        <v>1.689172733766009</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4600,7 +4600,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.107144939740793</v>
+        <v>4.965279802525769</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4608,22 +4608,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09165059479812362</v>
+        <v>0.09151209424582575</v>
       </c>
       <c r="C38">
-        <v>68.05065569623238</v>
+        <v>67.1902520363725</v>
       </c>
       <c r="D38">
-        <v>101.7814927572852</v>
+        <v>101.9944456824546</v>
       </c>
       <c r="E38">
-        <v>-10.09482144187172</v>
+        <v>-9.021464856842478</v>
       </c>
       <c r="F38">
-        <v>38.64083706105284</v>
+        <v>39.71419364608209</v>
       </c>
       <c r="G38">
         <v>4.91</v>
@@ -4644,28 +4644,28 @@
         <v>10.61</v>
       </c>
       <c r="M38">
-        <v>2.136838289476222</v>
+        <v>2.196194908628339</v>
       </c>
       <c r="N38">
-        <v>8.47316171052378</v>
+        <v>8.413805091371662</v>
       </c>
       <c r="O38">
-        <v>1.864095576315232</v>
+        <v>1.851037120101766</v>
       </c>
       <c r="P38">
-        <v>6.609066134208548</v>
+        <v>6.562767971269897</v>
       </c>
       <c r="Q38">
-        <v>12.11906613420855</v>
+        <v>12.0727679712699</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1189411793720682</v>
+        <v>0.119924625787025</v>
       </c>
       <c r="T38">
-        <v>1.689172733766009</v>
+        <v>1.711885122102195</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.965279802525771</v>
+        <v>4.831083051106155</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4690,22 +4690,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09151209424582575</v>
+        <v>0.09137359369352789</v>
       </c>
       <c r="C39">
-        <v>67.1902520363725</v>
+        <v>66.33074134885251</v>
       </c>
       <c r="D39">
-        <v>101.9944456824546</v>
+        <v>102.2082915799638</v>
       </c>
       <c r="E39">
-        <v>-9.021464856842478</v>
+        <v>-7.948108271813233</v>
       </c>
       <c r="F39">
-        <v>39.71419364608209</v>
+        <v>40.78755023111133</v>
       </c>
       <c r="G39">
         <v>4.91</v>
@@ -4726,28 +4726,28 @@
         <v>10.61</v>
       </c>
       <c r="M39">
-        <v>2.196194908628339</v>
+        <v>2.255551527780457</v>
       </c>
       <c r="N39">
-        <v>8.413805091371662</v>
+        <v>8.354448472219545</v>
       </c>
       <c r="O39">
-        <v>1.851037120101766</v>
+        <v>1.8379786638883</v>
       </c>
       <c r="P39">
-        <v>6.562767971269897</v>
+        <v>6.516469808331245</v>
       </c>
       <c r="Q39">
-        <v>12.0727679712699</v>
+        <v>12.02646980833125</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.119924625787025</v>
+        <v>0.1209397962798837</v>
       </c>
       <c r="T39">
-        <v>1.711885122102195</v>
+        <v>1.735330168126645</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.831083051106155</v>
+        <v>4.703949286603361</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4772,22 +4772,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09137359369352789</v>
+        <v>0.09123509314123004</v>
       </c>
       <c r="C40">
-        <v>66.33074134885251</v>
+        <v>65.47212926220493</v>
       </c>
       <c r="D40">
-        <v>102.2082915799638</v>
+        <v>102.4230360783455</v>
       </c>
       <c r="E40">
-        <v>-7.948108271813233</v>
+        <v>-6.874751686783988</v>
       </c>
       <c r="F40">
-        <v>40.78755023111133</v>
+        <v>41.86090681614058</v>
       </c>
       <c r="G40">
         <v>4.91</v>
@@ -4808,28 +4808,28 @@
         <v>10.61</v>
       </c>
       <c r="M40">
-        <v>2.255551527780457</v>
+        <v>2.314908146932574</v>
       </c>
       <c r="N40">
-        <v>8.354448472219545</v>
+        <v>8.295091853067428</v>
       </c>
       <c r="O40">
-        <v>1.8379786638883</v>
+        <v>1.824920207674834</v>
       </c>
       <c r="P40">
-        <v>6.516469808331245</v>
+        <v>6.470171645392593</v>
       </c>
       <c r="Q40">
-        <v>12.02646980833125</v>
+        <v>11.98017164539259</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1209397962798837</v>
+        <v>0.1219882510511968</v>
       </c>
       <c r="T40">
-        <v>1.735330168126645</v>
+        <v>1.759543904184683</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.703949286603361</v>
+        <v>4.58333520233148</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4854,22 +4854,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09123509314123004</v>
+        <v>0.09187659258893216</v>
       </c>
       <c r="C41">
-        <v>65.47212926220493</v>
+        <v>63.41164704222362</v>
       </c>
       <c r="D41">
-        <v>102.4230360783455</v>
+        <v>101.4359104433935</v>
       </c>
       <c r="E41">
-        <v>-6.874751686783988</v>
+        <v>-5.801395101754736</v>
       </c>
       <c r="F41">
-        <v>41.86090681614058</v>
+        <v>42.93426340116983</v>
       </c>
       <c r="G41">
         <v>4.91</v>
@@ -4890,45 +4890,45 @@
         <v>10.61</v>
       </c>
       <c r="M41">
-        <v>2.314908146932574</v>
+        <v>2.481600424587616</v>
       </c>
       <c r="N41">
-        <v>8.295091853067428</v>
+        <v>8.128399575412384</v>
       </c>
       <c r="O41">
-        <v>1.824920207674834</v>
+        <v>1.788247906590725</v>
       </c>
       <c r="P41">
-        <v>6.470171645392593</v>
+        <v>6.34015166882166</v>
       </c>
       <c r="Q41">
-        <v>11.98017164539259</v>
+        <v>11.85015166882166</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1219882510511968</v>
+        <v>0.123071654314887</v>
       </c>
       <c r="T41">
-        <v>1.759543904184683</v>
+        <v>1.78456476477799</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.58333520233148</v>
+        <v>4.275466708853071</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4936,22 +4936,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09187659258893216</v>
+        <v>0.09175759203663431</v>
       </c>
       <c r="C42">
-        <v>63.41164704222362</v>
+        <v>62.51996595076767</v>
       </c>
       <c r="D42">
-        <v>101.4359104433935</v>
+        <v>101.6175859369667</v>
       </c>
       <c r="E42">
-        <v>-5.801395101754736</v>
+        <v>-4.728038516725491</v>
       </c>
       <c r="F42">
-        <v>42.93426340116983</v>
+        <v>44.00761998619907</v>
       </c>
       <c r="G42">
         <v>4.91</v>
@@ -4972,28 +4972,28 @@
         <v>10.61</v>
       </c>
       <c r="M42">
-        <v>2.481600424587616</v>
+        <v>2.543640435202307</v>
       </c>
       <c r="N42">
-        <v>8.128399575412384</v>
+        <v>8.066359564797695</v>
       </c>
       <c r="O42">
-        <v>1.788247906590725</v>
+        <v>1.774599104255493</v>
       </c>
       <c r="P42">
-        <v>6.34015166882166</v>
+        <v>6.291760460542202</v>
       </c>
       <c r="Q42">
-        <v>11.85015166882166</v>
+        <v>11.8017604605422</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.123071654314887</v>
+        <v>0.1241917831129395</v>
       </c>
       <c r="T42">
-        <v>1.78456476477799</v>
+        <v>1.810433790137171</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.275466708853071</v>
+        <v>4.171187033027388</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5018,22 +5018,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09175759203663431</v>
+        <v>0.09163859148433645</v>
       </c>
       <c r="C43">
-        <v>62.51996595076767</v>
+        <v>61.62893680211651</v>
       </c>
       <c r="D43">
-        <v>101.6175859369667</v>
+        <v>101.7999133733448</v>
       </c>
       <c r="E43">
-        <v>-4.728038516725491</v>
+        <v>-3.654681931696246</v>
       </c>
       <c r="F43">
-        <v>44.00761998619907</v>
+        <v>45.08097657122832</v>
       </c>
       <c r="G43">
         <v>4.91</v>
@@ -5054,28 +5054,28 @@
         <v>10.61</v>
       </c>
       <c r="M43">
-        <v>2.543640435202307</v>
+        <v>2.605680445816997</v>
       </c>
       <c r="N43">
-        <v>8.066359564797695</v>
+        <v>8.004319554183004</v>
       </c>
       <c r="O43">
-        <v>1.774599104255493</v>
+        <v>1.760950301920261</v>
       </c>
       <c r="P43">
-        <v>6.291760460542202</v>
+        <v>6.243369252262744</v>
       </c>
       <c r="Q43">
-        <v>11.8017604605422</v>
+        <v>11.75336925226274</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1241917831129395</v>
+        <v>0.1253505370419594</v>
       </c>
       <c r="T43">
-        <v>1.810433790137171</v>
+        <v>1.837194850853566</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.171187033027388</v>
+        <v>4.071873056050545</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5100,22 +5100,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09163859148433645</v>
+        <v>0.09269349093203859</v>
       </c>
       <c r="C44">
-        <v>61.62893680211652</v>
+        <v>58.96175985971723</v>
       </c>
       <c r="D44">
-        <v>101.7999133733448</v>
+        <v>100.2060930159748</v>
       </c>
       <c r="E44">
-        <v>-3.654681931696253</v>
+        <v>-2.581325346667008</v>
       </c>
       <c r="F44">
-        <v>45.08097657122831</v>
+        <v>46.15433315625756</v>
       </c>
       <c r="G44">
         <v>4.91</v>
@@ -5136,45 +5136,45 @@
         <v>10.61</v>
       </c>
       <c r="M44">
-        <v>2.605680445816997</v>
+        <v>2.829260622478588</v>
       </c>
       <c r="N44">
-        <v>8.004319554183004</v>
+        <v>7.780739377521413</v>
       </c>
       <c r="O44">
-        <v>1.760950301920261</v>
+        <v>1.711762663054711</v>
       </c>
       <c r="P44">
-        <v>6.243369252262744</v>
+        <v>6.068976714466702</v>
       </c>
       <c r="Q44">
-        <v>11.75336925226274</v>
+        <v>11.5789767144667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1253505370419594</v>
+        <v>0.1265499490035765</v>
       </c>
       <c r="T44">
-        <v>1.837194850853566</v>
+        <v>1.864894896156501</v>
       </c>
       <c r="U44">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V44">
         <v>0.22</v>
       </c>
       <c r="W44">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.071873056050546</v>
+        <v>3.750096373484693</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5182,22 +5182,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09269349093203859</v>
+        <v>0.09260179037974073</v>
       </c>
       <c r="C45">
-        <v>58.96175985971723</v>
+        <v>58.02496797227627</v>
       </c>
       <c r="D45">
-        <v>100.2060930159748</v>
+        <v>100.3426577135631</v>
       </c>
       <c r="E45">
-        <v>-2.581325346667008</v>
+        <v>-1.507968761637756</v>
       </c>
       <c r="F45">
-        <v>46.15433315625756</v>
+        <v>47.22768974128681</v>
       </c>
       <c r="G45">
         <v>4.91</v>
@@ -5218,28 +5218,28 @@
         <v>10.61</v>
       </c>
       <c r="M45">
-        <v>2.829260622478588</v>
+        <v>2.895057381140882</v>
       </c>
       <c r="N45">
-        <v>7.780739377521413</v>
+        <v>7.714942618859119</v>
       </c>
       <c r="O45">
-        <v>1.711762663054711</v>
+        <v>1.697287376149006</v>
       </c>
       <c r="P45">
-        <v>6.068976714466702</v>
+        <v>6.017655242710113</v>
       </c>
       <c r="Q45">
-        <v>11.5789767144667</v>
+        <v>11.52765524271011</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1265499490035765</v>
+        <v>0.1277921971066799</v>
       </c>
       <c r="T45">
-        <v>1.864894896156501</v>
+        <v>1.893584228791683</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.750096373484693</v>
+        <v>3.66486691045095</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5264,22 +5264,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09260179037974073</v>
+        <v>0.09251008982744287</v>
       </c>
       <c r="C46">
-        <v>58.02496797227627</v>
+        <v>57.0885488240086</v>
       </c>
       <c r="D46">
-        <v>100.3426577135631</v>
+        <v>100.4795951503247</v>
       </c>
       <c r="E46">
-        <v>-1.507968761637756</v>
+        <v>-0.4346121766085105</v>
       </c>
       <c r="F46">
-        <v>47.22768974128681</v>
+        <v>48.30104632631605</v>
       </c>
       <c r="G46">
         <v>4.91</v>
@@ -5300,28 +5300,28 @@
         <v>10.61</v>
       </c>
       <c r="M46">
-        <v>2.895057381140882</v>
+        <v>2.960854139803174</v>
       </c>
       <c r="N46">
-        <v>7.714942618859119</v>
+        <v>7.649145860196827</v>
       </c>
       <c r="O46">
-        <v>1.697287376149006</v>
+        <v>1.682812089243302</v>
       </c>
       <c r="P46">
-        <v>6.017655242710113</v>
+        <v>5.966333770953525</v>
       </c>
       <c r="Q46">
-        <v>11.52765524271011</v>
+        <v>11.47633377095352</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1277921971066799</v>
+        <v>0.1290796178680779</v>
       </c>
       <c r="T46">
-        <v>1.893584228791683</v>
+        <v>1.923316809886326</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.66486691045095</v>
+        <v>3.58342542355204</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5346,22 +5346,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09251008982744287</v>
+        <v>0.09241838927514501</v>
       </c>
       <c r="C47">
-        <v>57.0885488240086</v>
+        <v>56.15250394302898</v>
       </c>
       <c r="D47">
-        <v>100.4795951503247</v>
+        <v>100.6169068543743</v>
       </c>
       <c r="E47">
-        <v>-0.4346121766085105</v>
+        <v>0.6387444084207345</v>
       </c>
       <c r="F47">
-        <v>48.30104632631605</v>
+        <v>49.3744029113453</v>
       </c>
       <c r="G47">
         <v>4.91</v>
@@ -5382,28 +5382,28 @@
         <v>10.61</v>
       </c>
       <c r="M47">
-        <v>2.960854139803174</v>
+        <v>3.026650898465467</v>
       </c>
       <c r="N47">
-        <v>7.649145860196827</v>
+        <v>7.583349101534534</v>
       </c>
       <c r="O47">
-        <v>1.682812089243302</v>
+        <v>1.668336802337598</v>
       </c>
       <c r="P47">
-        <v>5.966333770953525</v>
+        <v>5.915012299196936</v>
       </c>
       <c r="Q47">
-        <v>11.47633377095352</v>
+        <v>11.42501229919694</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1290796178680779</v>
+        <v>0.1304147208798981</v>
       </c>
       <c r="T47">
-        <v>1.923316809886326</v>
+        <v>1.954150597688179</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.58342542355204</v>
+        <v>3.505524870866126</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5428,22 +5428,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09241838927514501</v>
+        <v>0.09335316872284714</v>
       </c>
       <c r="C48">
-        <v>56.15250394302898</v>
+        <v>53.69676030815234</v>
       </c>
       <c r="D48">
-        <v>100.6169068543743</v>
+        <v>99.23451980452688</v>
       </c>
       <c r="E48">
-        <v>0.6387444084207345</v>
+        <v>1.71210099344998</v>
       </c>
       <c r="F48">
-        <v>49.3744029113453</v>
+        <v>50.44775949637454</v>
       </c>
       <c r="G48">
         <v>4.91</v>
@@ -5464,45 +5464,45 @@
         <v>10.61</v>
       </c>
       <c r="M48">
-        <v>3.026650898465467</v>
+        <v>3.233701383717609</v>
       </c>
       <c r="N48">
-        <v>7.583349101534534</v>
+        <v>7.376298616282392</v>
       </c>
       <c r="O48">
-        <v>1.668336802337598</v>
+        <v>1.622785695582126</v>
       </c>
       <c r="P48">
-        <v>5.915012299196936</v>
+        <v>5.753512920700266</v>
       </c>
       <c r="Q48">
-        <v>11.42501229919694</v>
+        <v>11.26351292070026</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1304147208798981</v>
+        <v>0.1318002051374474</v>
       </c>
       <c r="T48">
-        <v>1.954150597688179</v>
+        <v>1.986147924652366</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.22</v>
       </c>
       <c r="W48">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.505524870866126</v>
+        <v>3.281069814740366</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5510,22 +5510,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09335316872284714</v>
+        <v>0.09328330817054928</v>
       </c>
       <c r="C49">
-        <v>53.69676030815234</v>
+        <v>52.72540144799578</v>
       </c>
       <c r="D49">
-        <v>99.23451980452688</v>
+        <v>99.33651752939957</v>
       </c>
       <c r="E49">
-        <v>1.71210099344998</v>
+        <v>2.785457578479225</v>
       </c>
       <c r="F49">
-        <v>50.44775949637454</v>
+        <v>51.52111608140379</v>
       </c>
       <c r="G49">
         <v>4.91</v>
@@ -5546,28 +5546,28 @@
         <v>10.61</v>
       </c>
       <c r="M49">
-        <v>3.233701383717609</v>
+        <v>3.302503540817983</v>
       </c>
       <c r="N49">
-        <v>7.376298616282392</v>
+        <v>7.307496459182018</v>
       </c>
       <c r="O49">
-        <v>1.622785695582126</v>
+        <v>1.607649221020044</v>
       </c>
       <c r="P49">
-        <v>5.753512920700266</v>
+        <v>5.699847238161974</v>
       </c>
       <c r="Q49">
-        <v>11.26351292070026</v>
+        <v>11.20984723816197</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1318002051374474</v>
+        <v>0.1332389772510563</v>
       </c>
       <c r="T49">
-        <v>1.986147924652366</v>
+        <v>2.019375918038252</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.281069814740366</v>
+        <v>3.212714193599942</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5592,22 +5592,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09328330817054928</v>
+        <v>0.0932134476182514</v>
       </c>
       <c r="C50">
-        <v>52.72540144799578</v>
+        <v>51.75425247931906</v>
       </c>
       <c r="D50">
-        <v>99.33651752939957</v>
+        <v>99.4387251457521</v>
       </c>
       <c r="E50">
-        <v>2.785457578479225</v>
+        <v>3.85881416350847</v>
       </c>
       <c r="F50">
-        <v>51.52111608140379</v>
+        <v>52.59447266643303</v>
       </c>
       <c r="G50">
         <v>4.91</v>
@@ -5628,28 +5628,28 @@
         <v>10.61</v>
       </c>
       <c r="M50">
-        <v>3.302503540817983</v>
+        <v>3.371305697918358</v>
       </c>
       <c r="N50">
-        <v>7.307496459182018</v>
+        <v>7.238694302081644</v>
       </c>
       <c r="O50">
-        <v>1.607649221020044</v>
+        <v>1.592512746457962</v>
       </c>
       <c r="P50">
-        <v>5.699847238161974</v>
+        <v>5.646181555623683</v>
       </c>
       <c r="Q50">
-        <v>11.20984723816197</v>
+        <v>11.15618155562368</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1332389772510563</v>
+        <v>0.1347341718004929</v>
       </c>
       <c r="T50">
-        <v>2.019375918038252</v>
+        <v>2.05390696998829</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.212714193599942</v>
+        <v>3.147148597812189</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5674,22 +5674,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0932134476182514</v>
+        <v>0.09314358706595355</v>
       </c>
       <c r="C51">
-        <v>51.75425247931906</v>
+        <v>50.78331405066319</v>
       </c>
       <c r="D51">
-        <v>99.4387251457521</v>
+        <v>99.54114330212548</v>
       </c>
       <c r="E51">
-        <v>3.85881416350847</v>
+        <v>4.932170748537715</v>
       </c>
       <c r="F51">
-        <v>52.59447266643303</v>
+        <v>53.66782925146228</v>
       </c>
       <c r="G51">
         <v>4.91</v>
@@ -5710,28 +5710,28 @@
         <v>10.61</v>
       </c>
       <c r="M51">
-        <v>3.371305697918358</v>
+        <v>3.440107855018733</v>
       </c>
       <c r="N51">
-        <v>7.238694302081644</v>
+        <v>7.169892144981269</v>
       </c>
       <c r="O51">
-        <v>1.592512746457962</v>
+        <v>1.577376271895879</v>
       </c>
       <c r="P51">
-        <v>5.646181555623683</v>
+        <v>5.592515873085389</v>
       </c>
       <c r="Q51">
-        <v>11.15618155562368</v>
+        <v>11.10251587308539</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1347341718004929</v>
+        <v>0.1362891741319071</v>
       </c>
       <c r="T51">
-        <v>2.05390696998829</v>
+        <v>2.08981926401633</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5748,7 +5748,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.147148597812189</v>
+        <v>3.084205625855945</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5756,22 +5756,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09314358706595355</v>
+        <v>0.09307372651365568</v>
       </c>
       <c r="C52">
-        <v>50.78331405066319</v>
+        <v>49.81258681324391</v>
       </c>
       <c r="D52">
-        <v>99.54114330212548</v>
+        <v>99.64377264973544</v>
       </c>
       <c r="E52">
-        <v>4.932170748537715</v>
+        <v>6.00552733356696</v>
       </c>
       <c r="F52">
-        <v>53.66782925146228</v>
+        <v>54.74118583649152</v>
       </c>
       <c r="G52">
         <v>4.91</v>
@@ -5792,28 +5792,28 @@
         <v>10.61</v>
       </c>
       <c r="M52">
-        <v>3.440107855018733</v>
+        <v>3.508910012119107</v>
       </c>
       <c r="N52">
-        <v>7.169892144981269</v>
+        <v>7.101089987880894</v>
       </c>
       <c r="O52">
-        <v>1.577376271895879</v>
+        <v>1.562239797333797</v>
       </c>
       <c r="P52">
-        <v>5.592515873085389</v>
+        <v>5.538850190547098</v>
       </c>
       <c r="Q52">
-        <v>11.10251587308539</v>
+        <v>11.0488501905471</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1362891741319071</v>
+        <v>0.1379076459462361</v>
       </c>
       <c r="T52">
-        <v>2.08981926401633</v>
+        <v>2.127197365963883</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.084205625855945</v>
+        <v>3.023731005741122</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5838,22 +5838,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09307372651365568</v>
+        <v>0.09616754596135783</v>
       </c>
       <c r="C53">
-        <v>49.81258681324391</v>
+        <v>44.38820364943984</v>
       </c>
       <c r="D53">
-        <v>99.64377264973544</v>
+        <v>95.29274607096062</v>
       </c>
       <c r="E53">
-        <v>6.00552733356696</v>
+        <v>7.078883918596205</v>
       </c>
       <c r="F53">
-        <v>54.74118583649152</v>
+        <v>55.81454242152077</v>
       </c>
       <c r="G53">
         <v>4.91</v>
@@ -5874,45 +5874,45 @@
         <v>10.61</v>
       </c>
       <c r="M53">
-        <v>3.508910012119107</v>
+        <v>4.013065600107343</v>
       </c>
       <c r="N53">
-        <v>7.101089987880894</v>
+        <v>6.596934399892658</v>
       </c>
       <c r="O53">
-        <v>1.562239797333797</v>
+        <v>1.451325567976385</v>
       </c>
       <c r="P53">
-        <v>5.538850190547098</v>
+        <v>5.145608831916273</v>
       </c>
       <c r="Q53">
-        <v>11.0488501905471</v>
+        <v>10.65560883191627</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1379076459462361</v>
+        <v>0.1395935540861621</v>
       </c>
       <c r="T53">
-        <v>2.127197365963883</v>
+        <v>2.166132888825916</v>
       </c>
       <c r="U53">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V53">
         <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.023731005741122</v>
+        <v>2.643864082290656</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5920,22 +5920,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09616754596135783</v>
+        <v>0.09615852540905996</v>
       </c>
       <c r="C54">
-        <v>44.38820364943984</v>
+        <v>43.32698080974794</v>
       </c>
       <c r="D54">
-        <v>95.29274607096062</v>
+        <v>95.30487981629797</v>
       </c>
       <c r="E54">
-        <v>7.078883918596205</v>
+        <v>8.152240503625457</v>
       </c>
       <c r="F54">
-        <v>55.81454242152077</v>
+        <v>56.88789900655002</v>
       </c>
       <c r="G54">
         <v>4.91</v>
@@ -5956,28 +5956,28 @@
         <v>10.61</v>
       </c>
       <c r="M54">
-        <v>4.013065600107343</v>
+        <v>4.090239938570947</v>
       </c>
       <c r="N54">
-        <v>6.596934399892658</v>
+        <v>6.519760061429055</v>
       </c>
       <c r="O54">
-        <v>1.451325567976385</v>
+        <v>1.434347213514392</v>
       </c>
       <c r="P54">
-        <v>5.145608831916273</v>
+        <v>5.085412847914663</v>
       </c>
       <c r="Q54">
-        <v>10.65560883191627</v>
+        <v>10.59541284791466</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1395935540861621</v>
+        <v>0.1413512029979999</v>
       </c>
       <c r="T54">
-        <v>2.166132888825916</v>
+        <v>2.206725242448035</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.643864082290656</v>
+        <v>2.593979854322907</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6002,22 +6002,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09615852540905996</v>
+        <v>0.0961495048567621</v>
       </c>
       <c r="C55">
-        <v>43.32698080974794</v>
+        <v>42.26576106045967</v>
       </c>
       <c r="D55">
-        <v>95.30487981629797</v>
+        <v>95.31701665203894</v>
       </c>
       <c r="E55">
-        <v>8.152240503625457</v>
+        <v>9.225597088654702</v>
       </c>
       <c r="F55">
-        <v>56.88789900655002</v>
+        <v>57.96125559157927</v>
       </c>
       <c r="G55">
         <v>4.91</v>
@@ -6038,28 +6038,28 @@
         <v>10.61</v>
       </c>
       <c r="M55">
-        <v>4.090239938570947</v>
+        <v>4.16741427703455</v>
       </c>
       <c r="N55">
-        <v>6.519760061429055</v>
+        <v>6.442585722965451</v>
       </c>
       <c r="O55">
-        <v>1.434347213514392</v>
+        <v>1.417368859052399</v>
       </c>
       <c r="P55">
-        <v>5.085412847914663</v>
+        <v>5.025216863913052</v>
       </c>
       <c r="Q55">
-        <v>10.59541284791466</v>
+        <v>10.53521686391305</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1413512029979999</v>
+        <v>0.1431852714277437</v>
       </c>
       <c r="T55">
-        <v>2.206725242448035</v>
+        <v>2.249082481010247</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.593979854322907</v>
+        <v>2.545943190353964</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6084,22 +6084,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0961495048567621</v>
+        <v>0.09781358430446424</v>
       </c>
       <c r="C56">
-        <v>42.26576106045967</v>
+        <v>39.00455724219665</v>
       </c>
       <c r="D56">
-        <v>95.31701665203894</v>
+        <v>93.12916941880516</v>
       </c>
       <c r="E56">
-        <v>9.225597088654702</v>
+        <v>10.29895367368395</v>
       </c>
       <c r="F56">
-        <v>57.96125559157927</v>
+        <v>59.03461217660851</v>
       </c>
       <c r="G56">
         <v>4.91</v>
@@ -6120,45 +6120,45 @@
         <v>10.61</v>
       </c>
       <c r="M56">
-        <v>4.16741427703455</v>
+        <v>4.474823602986926</v>
       </c>
       <c r="N56">
-        <v>6.442585722965451</v>
+        <v>6.135176397013075</v>
       </c>
       <c r="O56">
-        <v>1.417368859052399</v>
+        <v>1.349738807342877</v>
       </c>
       <c r="P56">
-        <v>5.025216863913052</v>
+        <v>4.785437589670199</v>
       </c>
       <c r="Q56">
-        <v>10.53521686391305</v>
+        <v>10.2954375896702</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1431852714277437</v>
+        <v>0.1451008540099205</v>
       </c>
       <c r="T56">
-        <v>2.249082481010247</v>
+        <v>2.293322263508558</v>
       </c>
       <c r="U56">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V56">
         <v>0.22</v>
       </c>
       <c r="W56">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.545943190353964</v>
+        <v>2.371043183225786</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6166,22 +6166,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09781358430446424</v>
+        <v>0.09783498375216637</v>
       </c>
       <c r="C57">
-        <v>39.00455724219665</v>
+        <v>37.90371965171907</v>
       </c>
       <c r="D57">
-        <v>93.12916941880516</v>
+        <v>93.10168841335683</v>
       </c>
       <c r="E57">
-        <v>10.29895367368395</v>
+        <v>11.37231025871319</v>
       </c>
       <c r="F57">
-        <v>59.03461217660851</v>
+        <v>60.10796876163776</v>
       </c>
       <c r="G57">
         <v>4.91</v>
@@ -6202,28 +6202,28 @@
         <v>10.61</v>
       </c>
       <c r="M57">
-        <v>4.474823602986926</v>
+        <v>4.556184032132142</v>
       </c>
       <c r="N57">
-        <v>6.135176397013075</v>
+        <v>6.053815967867859</v>
       </c>
       <c r="O57">
-        <v>1.349738807342877</v>
+        <v>1.331839512930929</v>
       </c>
       <c r="P57">
-        <v>4.785437589670199</v>
+        <v>4.72197645493693</v>
       </c>
       <c r="Q57">
-        <v>10.2954375896702</v>
+        <v>10.23197645493693</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1451008540099205</v>
+        <v>0.1471035085276508</v>
       </c>
       <c r="T57">
-        <v>2.293322263508558</v>
+        <v>2.339572945211336</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6240,7 +6240,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.371043183225786</v>
+        <v>2.328703126382468</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6248,22 +6248,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09783498375216637</v>
+        <v>0.0978563831998685</v>
       </c>
       <c r="C58">
-        <v>37.90371965171907</v>
+        <v>36.8028982749129</v>
       </c>
       <c r="D58">
-        <v>93.10168841335683</v>
+        <v>93.0742236215799</v>
       </c>
       <c r="E58">
-        <v>11.37231025871319</v>
+        <v>12.44566684374244</v>
       </c>
       <c r="F58">
-        <v>60.10796876163776</v>
+        <v>61.181325346667</v>
       </c>
       <c r="G58">
         <v>4.91</v>
@@ -6284,28 +6284,28 @@
         <v>10.61</v>
       </c>
       <c r="M58">
-        <v>4.556184032132142</v>
+        <v>4.63754446127736</v>
       </c>
       <c r="N58">
-        <v>6.053815967867859</v>
+        <v>5.972455538722642</v>
       </c>
       <c r="O58">
-        <v>1.331839512930929</v>
+        <v>1.313940218518981</v>
       </c>
       <c r="P58">
-        <v>4.72197645493693</v>
+        <v>4.65851532020366</v>
       </c>
       <c r="Q58">
-        <v>10.23197645493693</v>
+        <v>10.16851532020366</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1471035085276508</v>
+        <v>0.1491993097671361</v>
       </c>
       <c r="T58">
-        <v>2.339572945211336</v>
+        <v>2.387974821411919</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6322,7 +6322,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.328703126382468</v>
+        <v>2.287848685568741</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6330,22 +6330,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0978563831998685</v>
+        <v>0.09787778264757066</v>
       </c>
       <c r="C59">
-        <v>36.8028982749129</v>
+        <v>35.70209309743336</v>
       </c>
       <c r="D59">
-        <v>93.0742236215799</v>
+        <v>93.04677502912962</v>
       </c>
       <c r="E59">
-        <v>12.44566684374244</v>
+        <v>13.51902342877169</v>
       </c>
       <c r="F59">
-        <v>61.181325346667</v>
+        <v>62.25468193169625</v>
       </c>
       <c r="G59">
         <v>4.91</v>
@@ -6366,28 +6366,28 @@
         <v>10.61</v>
       </c>
       <c r="M59">
-        <v>4.63754446127736</v>
+        <v>4.718904890422577</v>
       </c>
       <c r="N59">
-        <v>5.972455538722642</v>
+        <v>5.891095109577424</v>
       </c>
       <c r="O59">
-        <v>1.313940218518981</v>
+        <v>1.296040924107033</v>
       </c>
       <c r="P59">
-        <v>4.65851532020366</v>
+        <v>4.595054185470391</v>
       </c>
       <c r="Q59">
-        <v>10.16851532020366</v>
+        <v>10.10505418547039</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1491993097671361</v>
+        <v>0.1513949110656444</v>
       </c>
       <c r="T59">
-        <v>2.387974821411919</v>
+        <v>2.438681548860148</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.287848685568741</v>
+        <v>2.248403018576176</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6412,22 +6412,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09787778264757065</v>
+        <v>0.09789918209527279</v>
       </c>
       <c r="C60">
-        <v>35.70209309743339</v>
+        <v>34.6013041049527</v>
       </c>
       <c r="D60">
-        <v>93.04677502912963</v>
+        <v>93.01934262167819</v>
       </c>
       <c r="E60">
-        <v>13.51902342877167</v>
+        <v>14.59238001380092</v>
       </c>
       <c r="F60">
-        <v>62.25468193169624</v>
+        <v>63.32803851672548</v>
       </c>
       <c r="G60">
         <v>4.91</v>
@@ -6448,28 +6448,28 @@
         <v>10.61</v>
       </c>
       <c r="M60">
-        <v>4.718904890422575</v>
+        <v>4.800265319567792</v>
       </c>
       <c r="N60">
-        <v>5.891095109577426</v>
+        <v>5.809734680432209</v>
       </c>
       <c r="O60">
-        <v>1.296040924107034</v>
+        <v>1.278141629695086</v>
       </c>
       <c r="P60">
-        <v>4.595054185470392</v>
+        <v>4.531593050737123</v>
       </c>
       <c r="Q60">
-        <v>10.10505418547039</v>
+        <v>10.04159305073712</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1513949110656444</v>
+        <v>0.153697614866519</v>
       </c>
       <c r="T60">
-        <v>2.438681548860147</v>
+        <v>2.491861775208291</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.248403018576177</v>
+        <v>2.210294492837598</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6494,22 +6494,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09789918209527279</v>
+        <v>0.09792058154297492</v>
       </c>
       <c r="C61">
-        <v>34.6013041049527</v>
+        <v>33.50053128315989</v>
       </c>
       <c r="D61">
-        <v>93.01934262167819</v>
+        <v>92.99192638491462</v>
       </c>
       <c r="E61">
-        <v>14.59238001380092</v>
+        <v>15.66573659883016</v>
       </c>
       <c r="F61">
-        <v>63.32803851672548</v>
+        <v>64.40139510175473</v>
       </c>
       <c r="G61">
         <v>4.91</v>
@@ -6530,28 +6530,28 @@
         <v>10.61</v>
       </c>
       <c r="M61">
-        <v>4.800265319567792</v>
+        <v>4.881625748713009</v>
       </c>
       <c r="N61">
-        <v>5.809734680432209</v>
+        <v>5.728374251286993</v>
       </c>
       <c r="O61">
-        <v>1.278141629695086</v>
+        <v>1.260242335283138</v>
       </c>
       <c r="P61">
-        <v>4.531593050737123</v>
+        <v>4.468131916003854</v>
       </c>
       <c r="Q61">
-        <v>10.04159305073712</v>
+        <v>9.978131916003854</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.153697614866519</v>
+        <v>0.1561154538574373</v>
       </c>
       <c r="T61">
-        <v>2.491861775208291</v>
+        <v>2.547701012873841</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.210294492837598</v>
+        <v>2.173456251290304</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6576,22 +6576,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09792058154297492</v>
+        <v>0.09794198099067705</v>
       </c>
       <c r="C62">
-        <v>33.50053128315989</v>
+        <v>32.39977461776087</v>
       </c>
       <c r="D62">
-        <v>92.99192638491462</v>
+        <v>92.96452630454485</v>
       </c>
       <c r="E62">
-        <v>15.66573659883016</v>
+        <v>16.73909318385941</v>
       </c>
       <c r="F62">
-        <v>64.40139510175473</v>
+        <v>65.47475168678397</v>
       </c>
       <c r="G62">
         <v>4.91</v>
@@ -6612,28 +6612,28 @@
         <v>10.61</v>
       </c>
       <c r="M62">
-        <v>4.881625748713009</v>
+        <v>4.962986177858226</v>
       </c>
       <c r="N62">
-        <v>5.728374251286993</v>
+        <v>5.647013822141775</v>
       </c>
       <c r="O62">
-        <v>1.260242335283138</v>
+        <v>1.242343040871191</v>
       </c>
       <c r="P62">
-        <v>4.468131916003854</v>
+        <v>4.404670781270585</v>
       </c>
       <c r="Q62">
-        <v>9.978131916003854</v>
+        <v>9.914670781270583</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1561154538574373</v>
+        <v>0.1586572845914796</v>
       </c>
       <c r="T62">
-        <v>2.547701012873841</v>
+        <v>2.606403801188906</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.173456251290304</v>
+        <v>2.137825820941283</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6658,22 +6658,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09794198099067705</v>
+        <v>0.0979633804383792</v>
       </c>
       <c r="C63">
-        <v>32.39977461776087</v>
+        <v>31.29903409447836</v>
       </c>
       <c r="D63">
-        <v>92.96452630454485</v>
+        <v>92.93714236629158</v>
       </c>
       <c r="E63">
-        <v>16.73909318385941</v>
+        <v>17.81244976888865</v>
       </c>
       <c r="F63">
-        <v>65.47475168678397</v>
+        <v>66.54810827181322</v>
       </c>
       <c r="G63">
         <v>4.91</v>
@@ -6694,28 +6694,28 @@
         <v>10.61</v>
       </c>
       <c r="M63">
-        <v>4.962986177858226</v>
+        <v>5.044346607003442</v>
       </c>
       <c r="N63">
-        <v>5.647013822141775</v>
+        <v>5.565653392996559</v>
       </c>
       <c r="O63">
-        <v>1.242343040871191</v>
+        <v>1.224443746459243</v>
       </c>
       <c r="P63">
-        <v>4.404670781270585</v>
+        <v>4.341209646537316</v>
       </c>
       <c r="Q63">
-        <v>9.914670781270583</v>
+        <v>9.851209646537317</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1586572845914796</v>
+        <v>0.1613328958904716</v>
       </c>
       <c r="T63">
-        <v>2.606403801188906</v>
+        <v>2.668196209941607</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.137825820941283</v>
+        <v>2.103344759313198</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6740,22 +6740,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0979633804383792</v>
+        <v>0.09798477988608134</v>
       </c>
       <c r="C64">
-        <v>31.29903409447836</v>
+        <v>30.19830969905196</v>
       </c>
       <c r="D64">
-        <v>92.93714236629158</v>
+        <v>92.90977455589444</v>
       </c>
       <c r="E64">
-        <v>17.81244976888865</v>
+        <v>18.88580635391791</v>
       </c>
       <c r="F64">
-        <v>66.54810827181322</v>
+        <v>67.62146485684248</v>
       </c>
       <c r="G64">
         <v>4.91</v>
@@ -6776,28 +6776,28 @@
         <v>10.61</v>
       </c>
       <c r="M64">
-        <v>5.044346607003442</v>
+        <v>5.12570703614866</v>
       </c>
       <c r="N64">
-        <v>5.565653392996559</v>
+        <v>5.484292963851341</v>
       </c>
       <c r="O64">
-        <v>1.224443746459243</v>
+        <v>1.206544452047295</v>
       </c>
       <c r="P64">
-        <v>4.341209646537316</v>
+        <v>4.277748511804046</v>
       </c>
       <c r="Q64">
-        <v>9.851209646537317</v>
+        <v>9.787748511804047</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1613328958904716</v>
+        <v>0.1641531348272468</v>
       </c>
       <c r="T64">
-        <v>2.668196209941607</v>
+        <v>2.733328748897156</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6814,7 +6814,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.103344759313198</v>
+        <v>2.069958334562194</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6822,22 +6822,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09798477988608134</v>
+        <v>0.09800617933378347</v>
       </c>
       <c r="C65">
-        <v>30.19830969905196</v>
+        <v>29.0976014172381</v>
       </c>
       <c r="D65">
-        <v>92.90977455589444</v>
+        <v>92.88242285910982</v>
       </c>
       <c r="E65">
-        <v>18.88580635391791</v>
+        <v>19.95916293894716</v>
       </c>
       <c r="F65">
-        <v>67.62146485684248</v>
+        <v>68.69482144187172</v>
       </c>
       <c r="G65">
         <v>4.91</v>
@@ -6858,28 +6858,28 @@
         <v>10.61</v>
       </c>
       <c r="M65">
-        <v>5.12570703614866</v>
+        <v>5.207067465293878</v>
       </c>
       <c r="N65">
-        <v>5.484292963851341</v>
+        <v>5.402932534706124</v>
       </c>
       <c r="O65">
-        <v>1.206544452047295</v>
+        <v>1.188645157635347</v>
       </c>
       <c r="P65">
-        <v>4.277748511804046</v>
+        <v>4.214287377070777</v>
       </c>
       <c r="Q65">
-        <v>9.787748511804047</v>
+        <v>9.724287377070777</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1641531348272468</v>
+        <v>0.1671300537049541</v>
       </c>
       <c r="T65">
-        <v>2.733328748897156</v>
+        <v>2.802079762239125</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6896,7 +6896,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.069958334562194</v>
+        <v>2.03761523558466</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6904,22 +6904,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09800617933378347</v>
+        <v>0.0980275787814856</v>
       </c>
       <c r="C66">
-        <v>29.0976014172381</v>
+        <v>27.99690923480983</v>
       </c>
       <c r="D66">
-        <v>92.88242285910982</v>
+        <v>92.85508726171081</v>
       </c>
       <c r="E66">
-        <v>19.95916293894716</v>
+        <v>21.0325195239764</v>
       </c>
       <c r="F66">
-        <v>68.69482144187172</v>
+        <v>69.76817802690097</v>
       </c>
       <c r="G66">
         <v>4.91</v>
@@ -6940,28 +6940,28 @@
         <v>10.61</v>
       </c>
       <c r="M66">
-        <v>5.207067465293878</v>
+        <v>5.288427894439094</v>
       </c>
       <c r="N66">
-        <v>5.402932534706124</v>
+        <v>5.321572105560907</v>
       </c>
       <c r="O66">
-        <v>1.188645157635347</v>
+        <v>1.1707458632234</v>
       </c>
       <c r="P66">
-        <v>4.214287377070777</v>
+        <v>4.150826242337508</v>
       </c>
       <c r="Q66">
-        <v>9.724287377070777</v>
+        <v>9.660826242337507</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1671300537049541</v>
+        <v>0.170277082232816</v>
       </c>
       <c r="T66">
-        <v>2.802079762239125</v>
+        <v>2.87475940491492</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.03761523558466</v>
+        <v>2.006267308883357</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6986,22 +6986,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0980275787814856</v>
+        <v>0.1053591382291877</v>
       </c>
       <c r="C67">
-        <v>27.99690923480983</v>
+        <v>18.41855179919659</v>
       </c>
       <c r="D67">
-        <v>92.85508726171081</v>
+        <v>84.35008641112681</v>
       </c>
       <c r="E67">
-        <v>21.0325195239764</v>
+        <v>22.10587610900565</v>
       </c>
       <c r="F67">
-        <v>69.76817802690097</v>
+        <v>70.84153461193021</v>
       </c>
       <c r="G67">
         <v>4.91</v>
@@ -7022,45 +7022,45 @@
         <v>10.61</v>
       </c>
       <c r="M67">
-        <v>5.288427894439094</v>
+        <v>6.375738115073719</v>
       </c>
       <c r="N67">
-        <v>5.321572105560907</v>
+        <v>4.234261884926283</v>
       </c>
       <c r="O67">
-        <v>1.1707458632234</v>
+        <v>0.9315376146837822</v>
       </c>
       <c r="P67">
-        <v>4.150826242337508</v>
+        <v>3.3027242702425</v>
       </c>
       <c r="Q67">
-        <v>9.660826242337507</v>
+        <v>8.8127242702425</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.170277082232816</v>
+        <v>0.1736092300858463</v>
       </c>
       <c r="T67">
-        <v>2.87475940491492</v>
+        <v>2.951714320689292</v>
       </c>
       <c r="U67">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V67">
         <v>0.22</v>
       </c>
       <c r="W67">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.006267308883357</v>
+        <v>1.664121048967728</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7068,22 +7068,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1053591382291877</v>
+        <v>0.1054912976768899</v>
       </c>
       <c r="C68">
-        <v>18.41855179919659</v>
+        <v>17.20615527220026</v>
       </c>
       <c r="D68">
-        <v>84.35008641112681</v>
+        <v>84.21104646915973</v>
       </c>
       <c r="E68">
-        <v>22.10587610900565</v>
+        <v>23.17923269403489</v>
       </c>
       <c r="F68">
-        <v>70.84153461193021</v>
+        <v>71.91489119695946</v>
       </c>
       <c r="G68">
         <v>4.91</v>
@@ -7104,28 +7104,28 @@
         <v>10.61</v>
       </c>
       <c r="M68">
-        <v>6.375738115073719</v>
+        <v>6.472340207726351</v>
       </c>
       <c r="N68">
-        <v>4.234261884926283</v>
+        <v>4.13765979227365</v>
       </c>
       <c r="O68">
-        <v>0.9315376146837822</v>
+        <v>0.9102851543002031</v>
       </c>
       <c r="P68">
-        <v>3.3027242702425</v>
+        <v>3.227374637973448</v>
       </c>
       <c r="Q68">
-        <v>8.8127242702425</v>
+        <v>8.737374637973447</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1736092300858463</v>
+        <v>0.1771433262936057</v>
       </c>
       <c r="T68">
-        <v>2.951714320689292</v>
+        <v>3.033333170753019</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.664121048967728</v>
+        <v>1.639283421371195</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7150,22 +7150,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1054912976768899</v>
+        <v>0.105623457124592</v>
       </c>
       <c r="C69">
-        <v>17.20615527220026</v>
+        <v>15.99421636871827</v>
       </c>
       <c r="D69">
-        <v>84.21104646915973</v>
+        <v>84.07246415070698</v>
       </c>
       <c r="E69">
-        <v>23.17923269403489</v>
+        <v>24.25258927906414</v>
       </c>
       <c r="F69">
-        <v>71.91489119695946</v>
+        <v>72.9882477819887</v>
       </c>
       <c r="G69">
         <v>4.91</v>
@@ -7186,28 +7186,28 @@
         <v>10.61</v>
       </c>
       <c r="M69">
-        <v>6.472340207726351</v>
+        <v>6.568942300378983</v>
       </c>
       <c r="N69">
-        <v>4.13765979227365</v>
+        <v>4.041057699621018</v>
       </c>
       <c r="O69">
-        <v>0.9102851543002031</v>
+        <v>0.8890326939166241</v>
       </c>
       <c r="P69">
-        <v>3.227374637973448</v>
+        <v>3.152025005704394</v>
       </c>
       <c r="Q69">
-        <v>8.737374637973447</v>
+        <v>8.662025005704393</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1771433262936057</v>
+        <v>0.1808983035143501</v>
       </c>
       <c r="T69">
-        <v>3.033333170753019</v>
+        <v>3.12005319894573</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.639283421371195</v>
+        <v>1.615176312233383</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7232,22 +7232,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.105623457124592</v>
+        <v>0.1057556165722942</v>
       </c>
       <c r="C70">
-        <v>15.99421636871827</v>
+        <v>14.78273283319137</v>
       </c>
       <c r="D70">
-        <v>84.07246415070698</v>
+        <v>83.93433720020933</v>
       </c>
       <c r="E70">
-        <v>24.25258927906414</v>
+        <v>25.32594586409338</v>
       </c>
       <c r="F70">
-        <v>72.9882477819887</v>
+        <v>74.06160436701795</v>
       </c>
       <c r="G70">
         <v>4.91</v>
@@ -7268,28 +7268,28 @@
         <v>10.61</v>
       </c>
       <c r="M70">
-        <v>6.568942300378983</v>
+        <v>6.665544393031615</v>
       </c>
       <c r="N70">
-        <v>4.041057699621018</v>
+        <v>3.944455606968386</v>
       </c>
       <c r="O70">
-        <v>0.8890326939166241</v>
+        <v>0.867780233533045</v>
       </c>
       <c r="P70">
-        <v>3.152025005704394</v>
+        <v>3.076675373435341</v>
       </c>
       <c r="Q70">
-        <v>8.662025005704393</v>
+        <v>8.586675373435341</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1808983035143501</v>
+        <v>0.1848955373299812</v>
       </c>
       <c r="T70">
-        <v>3.12005319894573</v>
+        <v>3.212368067667002</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7306,7 +7306,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.615176312233383</v>
+        <v>1.591767959882175</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7314,22 +7314,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1057556165722942</v>
+        <v>0.1058877760199963</v>
       </c>
       <c r="C71">
-        <v>14.78273283319137</v>
+        <v>13.57170242485915</v>
       </c>
       <c r="D71">
-        <v>83.93433720020933</v>
+        <v>83.79666337690635</v>
       </c>
       <c r="E71">
-        <v>25.32594586409338</v>
+        <v>26.39930244912263</v>
       </c>
       <c r="F71">
-        <v>74.06160436701795</v>
+        <v>75.13496095204719</v>
       </c>
       <c r="G71">
         <v>4.91</v>
@@ -7350,28 +7350,28 @@
         <v>10.61</v>
       </c>
       <c r="M71">
-        <v>6.665544393031615</v>
+        <v>6.762146485684247</v>
       </c>
       <c r="N71">
-        <v>3.944455606968386</v>
+        <v>3.847853514315754</v>
       </c>
       <c r="O71">
-        <v>0.867780233533045</v>
+        <v>0.8465277731494659</v>
       </c>
       <c r="P71">
-        <v>3.076675373435341</v>
+        <v>3.001325741166288</v>
       </c>
       <c r="Q71">
-        <v>8.586675373435341</v>
+        <v>8.511325741166289</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1848955373299812</v>
+        <v>0.1891592533999877</v>
       </c>
       <c r="T71">
-        <v>3.212368067667002</v>
+        <v>3.310837260969692</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.591767959882175</v>
+        <v>1.569028417598143</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7396,22 +7396,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1058877760199963</v>
+        <v>0.1060199354676984</v>
       </c>
       <c r="C72">
-        <v>13.57170242485915</v>
+        <v>12.36112291763878</v>
       </c>
       <c r="D72">
-        <v>83.79666337690635</v>
+        <v>83.65944045471522</v>
       </c>
       <c r="E72">
-        <v>26.39930244912263</v>
+        <v>27.47265903415187</v>
       </c>
       <c r="F72">
-        <v>75.13496095204719</v>
+        <v>76.20831753707644</v>
       </c>
       <c r="G72">
         <v>4.91</v>
@@ -7432,28 +7432,28 @@
         <v>10.61</v>
       </c>
       <c r="M72">
-        <v>6.762146485684247</v>
+        <v>6.858748578336879</v>
       </c>
       <c r="N72">
-        <v>3.847853514315754</v>
+        <v>3.751251421663122</v>
       </c>
       <c r="O72">
-        <v>0.8465277731494659</v>
+        <v>0.8252753127658868</v>
       </c>
       <c r="P72">
-        <v>3.001325741166288</v>
+        <v>2.925976108897235</v>
       </c>
       <c r="Q72">
-        <v>8.511325741166289</v>
+        <v>8.435976108897234</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1891592533999877</v>
+        <v>0.1937170188541326</v>
       </c>
       <c r="T72">
-        <v>3.310837260969692</v>
+        <v>3.416097433120845</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.569028417598143</v>
+        <v>1.546929425800986</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7478,22 +7478,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1060199354676984</v>
+        <v>0.1061520949154006</v>
       </c>
       <c r="C73">
-        <v>12.36112291763878</v>
+        <v>11.15099210000506</v>
       </c>
       <c r="D73">
-        <v>83.65944045471522</v>
+        <v>83.52266622211074</v>
       </c>
       <c r="E73">
-        <v>27.47265903415187</v>
+        <v>28.54601561918112</v>
       </c>
       <c r="F73">
-        <v>76.20831753707644</v>
+        <v>77.28167412210568</v>
       </c>
       <c r="G73">
         <v>4.91</v>
@@ -7514,28 +7514,28 @@
         <v>10.61</v>
       </c>
       <c r="M73">
-        <v>6.858748578336879</v>
+        <v>6.955350670989511</v>
       </c>
       <c r="N73">
-        <v>3.751251421663122</v>
+        <v>3.65464932901049</v>
       </c>
       <c r="O73">
-        <v>0.8252753127658868</v>
+        <v>0.8040228523823078</v>
       </c>
       <c r="P73">
-        <v>2.925976108897235</v>
+        <v>2.850626476628182</v>
       </c>
       <c r="Q73">
-        <v>8.435976108897234</v>
+        <v>8.360626476628182</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1937170188541325</v>
+        <v>0.1986003389835735</v>
       </c>
       <c r="T73">
-        <v>3.416097433120843</v>
+        <v>3.528876188997078</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.546929425800986</v>
+        <v>1.525444294887084</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7560,22 +7560,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1061520949154006</v>
+        <v>0.1062842543631027</v>
       </c>
       <c r="C74">
-        <v>11.15099210000506</v>
+        <v>9.941307774871603</v>
       </c>
       <c r="D74">
-        <v>83.52266622211074</v>
+        <v>83.38633848200654</v>
       </c>
       <c r="E74">
-        <v>28.54601561918112</v>
+        <v>29.61937220421036</v>
       </c>
       <c r="F74">
-        <v>77.28167412210568</v>
+        <v>78.35503070713493</v>
       </c>
       <c r="G74">
         <v>4.91</v>
@@ -7596,28 +7596,28 @@
         <v>10.61</v>
       </c>
       <c r="M74">
-        <v>6.955350670989511</v>
+        <v>7.051952763642143</v>
       </c>
       <c r="N74">
-        <v>3.65464932901049</v>
+        <v>3.558047236357858</v>
       </c>
       <c r="O74">
-        <v>0.8040228523823078</v>
+        <v>0.7827703919987288</v>
       </c>
       <c r="P74">
-        <v>2.850626476628182</v>
+        <v>2.775276844359129</v>
       </c>
       <c r="Q74">
-        <v>8.360626476628182</v>
+        <v>8.285276844359128</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1986003389835735</v>
+        <v>0.20384538653001</v>
       </c>
       <c r="T74">
-        <v>3.528876188997078</v>
+        <v>3.65000892679007</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.525444294887084</v>
+        <v>1.50454779769685</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7642,22 +7642,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1062842543631027</v>
+        <v>0.1420990202529236</v>
       </c>
       <c r="C75">
-        <v>9.941307774871603</v>
+        <v>-16.70464699994382</v>
       </c>
       <c r="D75">
-        <v>83.38633848200654</v>
+        <v>57.81374029222035</v>
       </c>
       <c r="E75">
-        <v>29.61937220421036</v>
+        <v>30.69272878923961</v>
       </c>
       <c r="F75">
-        <v>78.35503070713493</v>
+        <v>79.42838729216417</v>
       </c>
       <c r="G75">
         <v>4.91</v>
@@ -7678,45 +7678,45 @@
         <v>10.61</v>
       </c>
       <c r="M75">
-        <v>7.051952763642143</v>
+        <v>11.6600872544897</v>
       </c>
       <c r="N75">
-        <v>3.558047236357858</v>
+        <v>-1.0500872544897</v>
       </c>
       <c r="O75">
-        <v>0.7827703919987288</v>
+        <v>-0.231019195987734</v>
       </c>
       <c r="P75">
-        <v>2.775276844359129</v>
+        <v>-0.819068058501966</v>
       </c>
       <c r="Q75">
-        <v>8.285276844359128</v>
+        <v>4.690931941498034</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.20384538653001</v>
+        <v>0.2123605927724381</v>
       </c>
       <c r="T75">
-        <v>3.65000892679007</v>
+        <v>3.846664960102498</v>
       </c>
       <c r="U75">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.22</v>
+        <v>0.2001871811980841</v>
       </c>
       <c r="W75">
-        <v>0.0702</v>
+        <v>0.1174125218001213</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.50454779769685</v>
+        <v>0.9099417327185639</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7724,22 +7724,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1420990202529236</v>
+        <v>0.1431090202529237</v>
       </c>
       <c r="C76">
-        <v>-16.70464699994382</v>
+        <v>-18.27371673689305</v>
       </c>
       <c r="D76">
-        <v>57.81374029222035</v>
+        <v>57.31802714030037</v>
       </c>
       <c r="E76">
-        <v>30.69272878923961</v>
+        <v>31.76608537426885</v>
       </c>
       <c r="F76">
-        <v>79.42838729216417</v>
+        <v>80.50174387719342</v>
       </c>
       <c r="G76">
         <v>4.91</v>
@@ -7760,37 +7760,37 @@
         <v>10.61</v>
       </c>
       <c r="M76">
-        <v>11.6600872544897</v>
+        <v>11.817656001172</v>
       </c>
       <c r="N76">
-        <v>-1.0500872544897</v>
+        <v>-1.207656001171994</v>
       </c>
       <c r="O76">
-        <v>-0.231019195987734</v>
+        <v>-0.2656843202578387</v>
       </c>
       <c r="P76">
-        <v>-0.819068058501966</v>
+        <v>-0.9419716809141554</v>
       </c>
       <c r="Q76">
-        <v>4.690931941498034</v>
+        <v>4.568028319085844</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2123605927724381</v>
+        <v>0.2190230164833357</v>
       </c>
       <c r="T76">
-        <v>3.846664960102498</v>
+        <v>4.000531558506599</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2001871811980841</v>
+        <v>0.1975180187821096</v>
       </c>
       <c r="W76">
-        <v>0.1174125218001213</v>
+        <v>0.1178043548427863</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9099417327185639</v>
+        <v>0.8978091762823163</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7806,22 +7806,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1431090202529237</v>
+        <v>0.1441190202529237</v>
       </c>
       <c r="C77">
-        <v>-18.27371673689305</v>
+        <v>-19.83435794246454</v>
       </c>
       <c r="D77">
-        <v>57.31802714030037</v>
+        <v>56.83074251975813</v>
       </c>
       <c r="E77">
-        <v>31.76608537426885</v>
+        <v>32.8394419592981</v>
       </c>
       <c r="F77">
-        <v>80.50174387719342</v>
+        <v>81.57510046222266</v>
       </c>
       <c r="G77">
         <v>4.91</v>
@@ -7842,37 +7842,37 @@
         <v>10.61</v>
       </c>
       <c r="M77">
-        <v>11.817656001172</v>
+        <v>11.97522474785429</v>
       </c>
       <c r="N77">
-        <v>-1.207656001171994</v>
+        <v>-1.365224747854286</v>
       </c>
       <c r="O77">
-        <v>-0.2656843202578387</v>
+        <v>-0.300349444527943</v>
       </c>
       <c r="P77">
-        <v>-0.9419716809141554</v>
+        <v>-1.064875303326343</v>
       </c>
       <c r="Q77">
-        <v>4.568028319085844</v>
+        <v>4.445124696673656</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2190230164833357</v>
+        <v>0.2262406421701413</v>
       </c>
       <c r="T77">
-        <v>4.000531558506599</v>
+        <v>4.167220373444374</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1975180187821096</v>
+        <v>0.194919097482345</v>
       </c>
       <c r="W77">
-        <v>0.1178043548427863</v>
+        <v>0.1181858764895918</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8978091762823163</v>
+        <v>0.8859958976470228</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7888,22 +7888,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1441190202529237</v>
+        <v>0.1451290202529237</v>
       </c>
       <c r="C78">
-        <v>-19.83435794246454</v>
+        <v>-21.3867837680239</v>
       </c>
       <c r="D78">
-        <v>56.83074251975813</v>
+        <v>56.35167327922801</v>
       </c>
       <c r="E78">
-        <v>32.8394419592981</v>
+        <v>33.91279854432734</v>
       </c>
       <c r="F78">
-        <v>81.57510046222266</v>
+        <v>82.64845704725191</v>
       </c>
       <c r="G78">
         <v>4.91</v>
@@ -7924,37 +7924,37 @@
         <v>10.61</v>
       </c>
       <c r="M78">
-        <v>11.97522474785429</v>
+        <v>12.13279349453658</v>
       </c>
       <c r="N78">
-        <v>-1.365224747854286</v>
+        <v>-1.522793494536581</v>
       </c>
       <c r="O78">
-        <v>-0.300349444527943</v>
+        <v>-0.3350145687980478</v>
       </c>
       <c r="P78">
-        <v>-1.064875303326343</v>
+        <v>-1.187778925738533</v>
       </c>
       <c r="Q78">
-        <v>4.445124696673656</v>
+        <v>4.322221074261467</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2262406421701413</v>
+        <v>0.2340858874818866</v>
       </c>
       <c r="T78">
-        <v>4.167220373444374</v>
+        <v>4.348403867941955</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.194919097482345</v>
+        <v>0.1923876806319249</v>
       </c>
       <c r="W78">
-        <v>0.1181858764895918</v>
+        <v>0.1185574884832334</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8859958976470228</v>
+        <v>0.8744894574178406</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7970,22 +7970,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1451290202529237</v>
+        <v>0.1461390202529237</v>
       </c>
       <c r="C79">
-        <v>-21.3867837680239</v>
+        <v>-22.9312002377619</v>
       </c>
       <c r="D79">
-        <v>56.35167327922801</v>
+        <v>55.88061339451926</v>
       </c>
       <c r="E79">
-        <v>33.91279854432734</v>
+        <v>34.98615512935659</v>
       </c>
       <c r="F79">
-        <v>82.64845704725191</v>
+        <v>83.72181363228115</v>
       </c>
       <c r="G79">
         <v>4.91</v>
@@ -8006,37 +8006,37 @@
         <v>10.61</v>
       </c>
       <c r="M79">
-        <v>12.13279349453658</v>
+        <v>12.29036224121887</v>
       </c>
       <c r="N79">
-        <v>-1.522793494536581</v>
+        <v>-1.680362241218873</v>
       </c>
       <c r="O79">
-        <v>-0.3350145687980478</v>
+        <v>-0.3696796930681521</v>
       </c>
       <c r="P79">
-        <v>-1.187778925738533</v>
+        <v>-1.310682548150721</v>
       </c>
       <c r="Q79">
-        <v>4.322221074261467</v>
+        <v>4.199317451849279</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2340858874818866</v>
+        <v>0.2426443369128815</v>
       </c>
       <c r="T79">
-        <v>4.348403867941955</v>
+        <v>4.546058589212044</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1923876806319249</v>
+        <v>0.1899211719058746</v>
       </c>
       <c r="W79">
-        <v>0.1185574884832334</v>
+        <v>0.1189195719642176</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8744894574178406</v>
+        <v>0.8632780541176119</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8052,22 +8052,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1461390202529237</v>
+        <v>0.1471490202529236</v>
       </c>
       <c r="C80">
-        <v>-22.9312002377619</v>
+        <v>-24.46780654411539</v>
       </c>
       <c r="D80">
-        <v>55.88061339451926</v>
+        <v>55.41736367319501</v>
       </c>
       <c r="E80">
-        <v>34.98615512935659</v>
+        <v>36.05951171438583</v>
       </c>
       <c r="F80">
-        <v>83.72181363228115</v>
+        <v>84.7951702173104</v>
       </c>
       <c r="G80">
         <v>4.91</v>
@@ -8088,37 +8088,37 @@
         <v>10.61</v>
       </c>
       <c r="M80">
-        <v>12.29036224121887</v>
+        <v>12.44793098790117</v>
       </c>
       <c r="N80">
-        <v>-1.680362241218873</v>
+        <v>-1.837930987901167</v>
       </c>
       <c r="O80">
-        <v>-0.3696796930681521</v>
+        <v>-0.4043448173382568</v>
       </c>
       <c r="P80">
-        <v>-1.310682548150721</v>
+        <v>-1.43358617056291</v>
       </c>
       <c r="Q80">
-        <v>4.199317451849279</v>
+        <v>4.076413829437089</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2426443369128815</v>
+        <v>0.2520178767658758</v>
       </c>
       <c r="T80">
-        <v>4.546058589212044</v>
+        <v>4.762537569650713</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1899211719058746</v>
+        <v>0.1875171064387116</v>
       </c>
       <c r="W80">
-        <v>0.1189195719642176</v>
+        <v>0.1192724887747971</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8632780541176119</v>
+        <v>0.8523504838123256</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8134,22 +8134,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1471490202529236</v>
+        <v>0.1481590202529237</v>
       </c>
       <c r="C81">
-        <v>-24.46780654411539</v>
+        <v>-25.99679532861509</v>
       </c>
       <c r="D81">
-        <v>55.41736367319501</v>
+        <v>54.96173147372457</v>
       </c>
       <c r="E81">
-        <v>36.05951171438583</v>
+        <v>37.13286829941509</v>
       </c>
       <c r="F81">
-        <v>84.7951702173104</v>
+        <v>85.86852680233966</v>
       </c>
       <c r="G81">
         <v>4.91</v>
@@ -8170,37 +8170,37 @@
         <v>10.61</v>
       </c>
       <c r="M81">
-        <v>12.44793098790117</v>
+        <v>12.60549973458346</v>
       </c>
       <c r="N81">
-        <v>-1.837930987901167</v>
+        <v>-1.995499734583461</v>
       </c>
       <c r="O81">
-        <v>-0.4043448173382568</v>
+        <v>-0.4390099416083615</v>
       </c>
       <c r="P81">
-        <v>-1.43358617056291</v>
+        <v>-1.5564897929751</v>
       </c>
       <c r="Q81">
-        <v>4.076413829437089</v>
+        <v>3.9535102070249</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2520178767658758</v>
+        <v>0.2623287706041696</v>
       </c>
       <c r="T81">
-        <v>4.762537569650713</v>
+        <v>5.000664448133249</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1875171064387116</v>
+        <v>0.1851731426082277</v>
       </c>
       <c r="W81">
-        <v>0.1192724887747971</v>
+        <v>0.1196165826651122</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8523504838123256</v>
+        <v>0.8416961027646714</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8216,22 +8216,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1481590202529237</v>
+        <v>0.1491690202529237</v>
       </c>
       <c r="C82">
-        <v>-25.99679532861509</v>
+        <v>-27.51835294899151</v>
       </c>
       <c r="D82">
-        <v>54.96173147372457</v>
+        <v>54.51353043837739</v>
       </c>
       <c r="E82">
-        <v>37.13286829941509</v>
+        <v>38.20622488444434</v>
       </c>
       <c r="F82">
-        <v>85.86852680233966</v>
+        <v>86.9418833873689</v>
       </c>
       <c r="G82">
         <v>4.91</v>
@@ -8252,37 +8252,37 @@
         <v>10.61</v>
       </c>
       <c r="M82">
-        <v>12.60549973458346</v>
+        <v>12.76306848126576</v>
       </c>
       <c r="N82">
-        <v>-1.995499734583461</v>
+        <v>-2.153068481265755</v>
       </c>
       <c r="O82">
-        <v>-0.4390099416083615</v>
+        <v>-0.4736750658784662</v>
       </c>
       <c r="P82">
-        <v>-1.5564897929751</v>
+        <v>-1.679393415387289</v>
       </c>
       <c r="Q82">
-        <v>3.9535102070249</v>
+        <v>3.830606584612711</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2623287706041696</v>
+        <v>0.2737250216885996</v>
       </c>
       <c r="T82">
-        <v>5.000664448133249</v>
+        <v>5.263857313824472</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1851731426082277</v>
+        <v>0.1828870544278792</v>
       </c>
       <c r="W82">
-        <v>0.1196165826651122</v>
+        <v>0.1199521804099873</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8416961027646714</v>
+        <v>0.8313047928539965</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8298,22 +8298,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1491690202529237</v>
+        <v>0.1501790202529237</v>
       </c>
       <c r="C83">
-        <v>-27.51835294899151</v>
+        <v>-29.03265973331777</v>
       </c>
       <c r="D83">
-        <v>54.51353043837739</v>
+        <v>54.07258023908038</v>
       </c>
       <c r="E83">
-        <v>38.20622488444434</v>
+        <v>39.27958146947358</v>
       </c>
       <c r="F83">
-        <v>86.9418833873689</v>
+        <v>88.01523997239815</v>
       </c>
       <c r="G83">
         <v>4.91</v>
@@ -8334,37 +8334,37 @@
         <v>10.61</v>
       </c>
       <c r="M83">
-        <v>12.76306848126576</v>
+        <v>12.92063722794805</v>
       </c>
       <c r="N83">
-        <v>-2.153068481265755</v>
+        <v>-2.310637227948048</v>
       </c>
       <c r="O83">
-        <v>-0.4736750658784662</v>
+        <v>-0.5083401901485706</v>
       </c>
       <c r="P83">
-        <v>-1.679393415387289</v>
+        <v>-1.802297037799477</v>
       </c>
       <c r="Q83">
-        <v>3.830606584612711</v>
+        <v>3.707702962200523</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2737250216885996</v>
+        <v>0.2863875228935219</v>
       </c>
       <c r="T83">
-        <v>5.263857313824472</v>
+        <v>5.556293831259167</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1828870544278792</v>
+        <v>0.1806567244958319</v>
       </c>
       <c r="W83">
-        <v>0.1199521804099873</v>
+        <v>0.1202795928440119</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8313047928539965</v>
+        <v>0.8211669295265087</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8380,22 +8380,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1501790202529237</v>
+        <v>0.1511890202529237</v>
       </c>
       <c r="C84">
-        <v>-29.03265973331777</v>
+        <v>-30.53989022191698</v>
       </c>
       <c r="D84">
-        <v>54.07258023908038</v>
+        <v>53.63870633551042</v>
       </c>
       <c r="E84">
-        <v>39.27958146947358</v>
+        <v>40.35293805450283</v>
       </c>
       <c r="F84">
-        <v>88.01523997239815</v>
+        <v>89.08859655742739</v>
       </c>
       <c r="G84">
         <v>4.91</v>
@@ -8416,37 +8416,37 @@
         <v>10.61</v>
       </c>
       <c r="M84">
-        <v>12.92063722794805</v>
+        <v>13.07820597463034</v>
       </c>
       <c r="N84">
-        <v>-2.310637227948048</v>
+        <v>-2.468205974630342</v>
       </c>
       <c r="O84">
-        <v>-0.5083401901485706</v>
+        <v>-0.5430053144186753</v>
       </c>
       <c r="P84">
-        <v>-1.802297037799477</v>
+        <v>-1.925200660211667</v>
       </c>
       <c r="Q84">
-        <v>3.707702962200523</v>
+        <v>3.584799339788333</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2863875228935219</v>
+        <v>0.3005397301225526</v>
       </c>
       <c r="T84">
-        <v>5.556293831259167</v>
+        <v>5.883134644862647</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1806567244958319</v>
+        <v>0.1784801374537134</v>
       </c>
       <c r="W84">
-        <v>0.1202795928440119</v>
+        <v>0.1205991158217949</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8211669295265087</v>
+        <v>0.8112733520623339</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8462,22 +8462,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1511890202529237</v>
+        <v>0.1521990202529237</v>
       </c>
       <c r="C85">
-        <v>-30.53989022191698</v>
+        <v>-32.04021339771586</v>
       </c>
       <c r="D85">
-        <v>53.63870633551042</v>
+        <v>53.21173974474078</v>
       </c>
       <c r="E85">
-        <v>40.35293805450283</v>
+        <v>41.42629463953207</v>
       </c>
       <c r="F85">
-        <v>89.08859655742739</v>
+        <v>90.16195314245664</v>
       </c>
       <c r="G85">
         <v>4.91</v>
@@ -8498,37 +8498,37 @@
         <v>10.61</v>
       </c>
       <c r="M85">
-        <v>13.07820597463034</v>
+        <v>13.23577472131264</v>
       </c>
       <c r="N85">
-        <v>-2.468205974630342</v>
+        <v>-2.625774721312634</v>
       </c>
       <c r="O85">
-        <v>-0.5430053144186753</v>
+        <v>-0.5776704386887795</v>
       </c>
       <c r="P85">
-        <v>-1.925200660211667</v>
+        <v>-2.048104282623855</v>
       </c>
       <c r="Q85">
-        <v>3.584799339788333</v>
+        <v>3.461895717376145</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3005397301225526</v>
+        <v>0.3164609632552122</v>
       </c>
       <c r="T85">
-        <v>5.883134644862647</v>
+        <v>6.250830560166564</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1784801374537134</v>
+        <v>0.1763553739125978</v>
       </c>
       <c r="W85">
-        <v>0.1205991158217949</v>
+        <v>0.1209110311096307</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8112733520623339</v>
+        <v>0.8016153359663538</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8544,22 +8544,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1521990202529237</v>
+        <v>0.2011342516784251</v>
       </c>
       <c r="C86">
-        <v>-32.04021339771585</v>
+        <v>-47.9238582437102</v>
       </c>
       <c r="D86">
-        <v>53.21173974474078</v>
+        <v>38.40145148377567</v>
       </c>
       <c r="E86">
-        <v>41.42629463953206</v>
+        <v>42.4996512245613</v>
       </c>
       <c r="F86">
-        <v>90.16195314245662</v>
+        <v>91.23530972748587</v>
       </c>
       <c r="G86">
         <v>4.91</v>
@@ -8580,45 +8580,45 @@
         <v>10.61</v>
       </c>
       <c r="M86">
-        <v>13.23577472131263</v>
+        <v>18.32005019327916</v>
       </c>
       <c r="N86">
-        <v>-2.625774721312633</v>
+        <v>-7.710050193279161</v>
       </c>
       <c r="O86">
-        <v>-0.5776704386887792</v>
+        <v>-1.696211042521415</v>
       </c>
       <c r="P86">
-        <v>-2.048104282623854</v>
+        <v>-6.013839150757745</v>
       </c>
       <c r="Q86">
-        <v>3.461895717376146</v>
+        <v>-0.5038391507577451</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.316460963255212</v>
+        <v>0.3480065703089024</v>
       </c>
       <c r="T86">
-        <v>6.25083056016656</v>
+        <v>6.979366519836083</v>
       </c>
       <c r="U86">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1763553739125979</v>
+        <v>0.1274123146702031</v>
       </c>
       <c r="W86">
-        <v>0.1209110311096307</v>
+        <v>0.1752156072142232</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.8016153359663539</v>
+        <v>0.5791468848645597</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8626,22 +8626,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2011342516784251</v>
+        <v>0.2026842516784251</v>
       </c>
       <c r="C87">
-        <v>-47.9238582437102</v>
+        <v>-49.33279928058781</v>
       </c>
       <c r="D87">
-        <v>38.40145148377567</v>
+        <v>38.0658670319273</v>
       </c>
       <c r="E87">
-        <v>42.4996512245613</v>
+        <v>43.57300780959055</v>
       </c>
       <c r="F87">
-        <v>91.23530972748587</v>
+        <v>92.30866631251511</v>
       </c>
       <c r="G87">
         <v>4.91</v>
@@ -8662,37 +8662,37 @@
         <v>10.61</v>
       </c>
       <c r="M87">
-        <v>18.32005019327916</v>
+        <v>18.53558019555303</v>
       </c>
       <c r="N87">
-        <v>-7.710050193279161</v>
+        <v>-7.925580195553033</v>
       </c>
       <c r="O87">
-        <v>-1.696211042521415</v>
+        <v>-1.743627643021667</v>
       </c>
       <c r="P87">
-        <v>-6.013839150757745</v>
+        <v>-6.181952552531366</v>
       </c>
       <c r="Q87">
-        <v>-0.5038391507577451</v>
+        <v>-0.6719525525313665</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3480065703089024</v>
+        <v>0.3695927539023954</v>
       </c>
       <c r="T87">
-        <v>6.979366519836083</v>
+        <v>7.477892699824375</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1274123146702031</v>
+        <v>0.1259307761275263</v>
       </c>
       <c r="W87">
-        <v>0.1752156072142232</v>
+        <v>0.1755131001535927</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5791468848645597</v>
+        <v>0.5724126187614834</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8708,22 +8708,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2026842516784251</v>
+        <v>0.2042342516784251</v>
       </c>
       <c r="C88">
-        <v>-49.33279928058781</v>
+        <v>-50.73592588579285</v>
       </c>
       <c r="D88">
-        <v>38.0658670319273</v>
+        <v>37.73609701175151</v>
       </c>
       <c r="E88">
-        <v>43.57300780959055</v>
+        <v>44.64636439461979</v>
       </c>
       <c r="F88">
-        <v>92.30866631251511</v>
+        <v>93.38202289754436</v>
       </c>
       <c r="G88">
         <v>4.91</v>
@@ -8744,37 +8744,37 @@
         <v>10.61</v>
       </c>
       <c r="M88">
-        <v>18.53558019555303</v>
+        <v>18.75111019782691</v>
       </c>
       <c r="N88">
-        <v>-7.925580195553033</v>
+        <v>-8.141110197826906</v>
       </c>
       <c r="O88">
-        <v>-1.743627643021667</v>
+        <v>-1.791044243521919</v>
       </c>
       <c r="P88">
-        <v>-6.181952552531366</v>
+        <v>-6.350065954304987</v>
       </c>
       <c r="Q88">
-        <v>-0.6719525525313665</v>
+        <v>-0.8400659543049871</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3695927539023954</v>
+        <v>0.3944998888179643</v>
       </c>
       <c r="T88">
-        <v>7.477892699824375</v>
+        <v>8.053115215195481</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1259307761275263</v>
+        <v>0.1244832959421525</v>
       </c>
       <c r="W88">
-        <v>0.1755131001535927</v>
+        <v>0.1758037541748158</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5724126187614834</v>
+        <v>0.5658331633734204</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8790,22 +8790,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2042342516784251</v>
+        <v>0.2057842516784251</v>
       </c>
       <c r="C89">
-        <v>-50.73592588579285</v>
+        <v>-52.13338787519486</v>
       </c>
       <c r="D89">
-        <v>37.73609701175151</v>
+        <v>37.41199160737876</v>
       </c>
       <c r="E89">
-        <v>44.64636439461979</v>
+        <v>45.71972097964905</v>
       </c>
       <c r="F89">
-        <v>93.38202289754436</v>
+        <v>94.45537948257362</v>
       </c>
       <c r="G89">
         <v>4.91</v>
@@ -8826,37 +8826,37 @@
         <v>10.61</v>
       </c>
       <c r="M89">
-        <v>18.75111019782691</v>
+        <v>18.96664020010078</v>
       </c>
       <c r="N89">
-        <v>-8.141110197826906</v>
+        <v>-8.356640200100783</v>
       </c>
       <c r="O89">
-        <v>-1.791044243521919</v>
+        <v>-1.838460844022172</v>
       </c>
       <c r="P89">
-        <v>-6.350065954304987</v>
+        <v>-6.51817935607861</v>
       </c>
       <c r="Q89">
-        <v>-0.8400659543049871</v>
+        <v>-1.00817935607861</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3944998888179643</v>
+        <v>0.423558212886128</v>
       </c>
       <c r="T89">
-        <v>8.053115215195481</v>
+        <v>8.724208149795105</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1244832959421525</v>
+        <v>0.1230687130337189</v>
       </c>
       <c r="W89">
-        <v>0.1758037541748158</v>
+        <v>0.1760878024228293</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5658331633734204</v>
+        <v>0.5594032410623586</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8872,22 +8872,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2057842516784251</v>
+        <v>0.2073342516784251</v>
       </c>
       <c r="C90">
-        <v>-52.13338787519486</v>
+        <v>-53.52532996157611</v>
       </c>
       <c r="D90">
-        <v>37.41199160737876</v>
+        <v>37.09340610602676</v>
       </c>
       <c r="E90">
-        <v>45.71972097964905</v>
+        <v>46.7930775646783</v>
       </c>
       <c r="F90">
-        <v>94.45537948257362</v>
+        <v>95.52873606760286</v>
       </c>
       <c r="G90">
         <v>4.91</v>
@@ -8908,37 +8908,37 @@
         <v>10.61</v>
       </c>
       <c r="M90">
-        <v>18.96664020010078</v>
+        <v>19.18217020237466</v>
       </c>
       <c r="N90">
-        <v>-8.356640200100783</v>
+        <v>-8.572170202374656</v>
       </c>
       <c r="O90">
-        <v>-1.838460844022172</v>
+        <v>-1.885877444522424</v>
       </c>
       <c r="P90">
-        <v>-6.51817935607861</v>
+        <v>-6.686292757852232</v>
       </c>
       <c r="Q90">
-        <v>-1.00817935607861</v>
+        <v>-1.176292757852232</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.423558212886128</v>
+        <v>0.4578998686030488</v>
       </c>
       <c r="T90">
-        <v>8.724208149795105</v>
+        <v>9.517317981594662</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1230687130337189</v>
+        <v>0.1216859185052502</v>
       </c>
       <c r="W90">
-        <v>0.1760878024228293</v>
+        <v>0.1763654675641458</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5594032410623586</v>
+        <v>0.5531178113875006</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8954,22 +8954,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2073342516784251</v>
+        <v>0.2088842516784251</v>
       </c>
       <c r="C91">
-        <v>-53.52532996157611</v>
+        <v>-54.91189197007625</v>
       </c>
       <c r="D91">
-        <v>37.09340610602676</v>
+        <v>36.78020068255586</v>
       </c>
       <c r="E91">
-        <v>46.7930775646783</v>
+        <v>47.86643414970754</v>
       </c>
       <c r="F91">
-        <v>95.52873606760286</v>
+        <v>96.60209265263211</v>
       </c>
       <c r="G91">
         <v>4.91</v>
@@ -8990,37 +8990,37 @@
         <v>10.61</v>
       </c>
       <c r="M91">
-        <v>19.18217020237466</v>
+        <v>19.39770020464853</v>
       </c>
       <c r="N91">
-        <v>-8.572170202374656</v>
+        <v>-8.787700204648528</v>
       </c>
       <c r="O91">
-        <v>-1.885877444522424</v>
+        <v>-1.933294045022676</v>
       </c>
       <c r="P91">
-        <v>-6.686292757852232</v>
+        <v>-6.854406159625852</v>
       </c>
       <c r="Q91">
-        <v>-1.176292757852232</v>
+        <v>-1.344406159625852</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4578998686030488</v>
+        <v>0.4991098554633537</v>
       </c>
       <c r="T91">
-        <v>9.517317981594662</v>
+        <v>10.46904977975413</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1216859185052502</v>
+        <v>0.1203338527440807</v>
       </c>
       <c r="W91">
-        <v>0.1763654675641458</v>
+        <v>0.1766369623689886</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5531178113875006</v>
+        <v>0.5469720579276396</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9036,22 +9036,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2088842516784251</v>
+        <v>0.2104342516784251</v>
       </c>
       <c r="C92">
-        <v>-54.91189197007625</v>
+        <v>-56.29320904281342</v>
       </c>
       <c r="D92">
-        <v>36.78020068255586</v>
+        <v>36.47224019484794</v>
       </c>
       <c r="E92">
-        <v>47.86643414970754</v>
+        <v>48.93979073473679</v>
       </c>
       <c r="F92">
-        <v>96.60209265263211</v>
+        <v>97.67544923766135</v>
       </c>
       <c r="G92">
         <v>4.91</v>
@@ -9072,37 +9072,37 @@
         <v>10.61</v>
       </c>
       <c r="M92">
-        <v>19.39770020464853</v>
+        <v>19.6132302069224</v>
       </c>
       <c r="N92">
-        <v>-8.787700204648528</v>
+        <v>-9.003230206922398</v>
       </c>
       <c r="O92">
-        <v>-1.933294045022676</v>
+        <v>-1.980710645522928</v>
       </c>
       <c r="P92">
-        <v>-6.854406159625852</v>
+        <v>-7.02251956139947</v>
       </c>
       <c r="Q92">
-        <v>-1.344406159625852</v>
+        <v>-1.51251956139947</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4991098554633537</v>
+        <v>0.5494776171815041</v>
       </c>
       <c r="T92">
-        <v>10.46904977975413</v>
+        <v>11.63227753306014</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1203338527440807</v>
+        <v>0.119011502713926</v>
       </c>
       <c r="W92">
-        <v>0.1766369623689886</v>
+        <v>0.1769024902550436</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5469720579276396</v>
+        <v>0.5409613759723908</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9118,22 +9118,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2104342516784251</v>
+        <v>0.2119842516784251</v>
       </c>
       <c r="C93">
-        <v>-56.29320904281342</v>
+        <v>-57.66941183331083</v>
       </c>
       <c r="D93">
-        <v>36.47224019484794</v>
+        <v>36.16939398937977</v>
       </c>
       <c r="E93">
-        <v>48.93979073473679</v>
+        <v>50.01314731976603</v>
       </c>
       <c r="F93">
-        <v>97.67544923766135</v>
+        <v>98.7488058226906</v>
       </c>
       <c r="G93">
         <v>4.91</v>
@@ -9154,37 +9154,37 @@
         <v>10.61</v>
       </c>
       <c r="M93">
-        <v>19.6132302069224</v>
+        <v>19.82876020919627</v>
       </c>
       <c r="N93">
-        <v>-9.003230206922398</v>
+        <v>-9.218760209196271</v>
       </c>
       <c r="O93">
-        <v>-1.980710645522928</v>
+        <v>-2.02812724602318</v>
       </c>
       <c r="P93">
-        <v>-7.02251956139947</v>
+        <v>-7.190632963173091</v>
       </c>
       <c r="Q93">
-        <v>-1.51251956139947</v>
+        <v>-1.680632963173091</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5494776171815041</v>
+        <v>0.6124373193291923</v>
       </c>
       <c r="T93">
-        <v>11.63227753306014</v>
+        <v>13.08631222469267</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.119011502713926</v>
+        <v>0.1177178994235572</v>
       </c>
       <c r="W93">
-        <v>0.1769024902550436</v>
+        <v>0.1771622457957497</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5409613759723908</v>
+        <v>0.5350813610161692</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9200,22 +9200,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2119842516784251</v>
+        <v>0.2135342516784251</v>
       </c>
       <c r="C94">
-        <v>-57.66941183331083</v>
+        <v>-59.04062669131676</v>
       </c>
       <c r="D94">
-        <v>36.16939398937977</v>
+        <v>35.87153571640309</v>
       </c>
       <c r="E94">
-        <v>50.01314731976603</v>
+        <v>51.08650390479528</v>
       </c>
       <c r="F94">
-        <v>98.7488058226906</v>
+        <v>99.82216240771984</v>
       </c>
       <c r="G94">
         <v>4.91</v>
@@ -9236,37 +9236,37 @@
         <v>10.61</v>
       </c>
       <c r="M94">
-        <v>19.82876020919627</v>
+        <v>20.04429021147014</v>
       </c>
       <c r="N94">
-        <v>-9.218760209196271</v>
+        <v>-9.434290211470143</v>
       </c>
       <c r="O94">
-        <v>-2.02812724602318</v>
+        <v>-2.075543846523431</v>
       </c>
       <c r="P94">
-        <v>-7.190632963173091</v>
+        <v>-7.358746364946712</v>
       </c>
       <c r="Q94">
-        <v>-1.680632963173091</v>
+        <v>-1.848746364946712</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6124373193291923</v>
+        <v>0.6933855078047912</v>
       </c>
       <c r="T94">
-        <v>13.08631222469267</v>
+        <v>14.95578539964876</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1177178994235572</v>
+        <v>0.1164521155587878</v>
       </c>
       <c r="W94">
-        <v>0.1771622457957497</v>
+        <v>0.1774164151957954</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5350813610161692</v>
+        <v>0.5293277979944899</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9282,22 +9282,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2135342516784251</v>
+        <v>0.2150842516784251</v>
       </c>
       <c r="C95">
-        <v>-59.04062669131676</v>
+        <v>-60.40697583856705</v>
       </c>
       <c r="D95">
-        <v>35.87153571640309</v>
+        <v>35.57854315418204</v>
       </c>
       <c r="E95">
-        <v>51.08650390479528</v>
+        <v>52.15986048982452</v>
       </c>
       <c r="F95">
-        <v>99.82216240771984</v>
+        <v>100.8955189927491</v>
       </c>
       <c r="G95">
         <v>4.91</v>
@@ -9318,37 +9318,37 @@
         <v>10.61</v>
       </c>
       <c r="M95">
-        <v>20.04429021147014</v>
+        <v>20.25982021374402</v>
       </c>
       <c r="N95">
-        <v>-9.434290211470143</v>
+        <v>-9.649820213744016</v>
       </c>
       <c r="O95">
-        <v>-2.075543846523431</v>
+        <v>-2.122960447023684</v>
       </c>
       <c r="P95">
-        <v>-7.358746364946712</v>
+        <v>-7.526859766720333</v>
       </c>
       <c r="Q95">
-        <v>-1.848746364946712</v>
+        <v>-2.016859766720333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6933855078047912</v>
+        <v>0.8013164257722565</v>
       </c>
       <c r="T95">
-        <v>14.95578539964876</v>
+        <v>17.44841629959022</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1164521155587878</v>
+        <v>0.1152132632656092</v>
       </c>
       <c r="W95">
-        <v>0.1774164151957954</v>
+        <v>0.1776651767362657</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5293277979944899</v>
+        <v>0.5236966512073145</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9364,22 +9364,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2150842516784251</v>
+        <v>0.2166342516784251</v>
       </c>
       <c r="C96">
-        <v>-60.40697583856705</v>
+        <v>-61.76857753600379</v>
       </c>
       <c r="D96">
-        <v>35.57854315418204</v>
+        <v>35.29029804177454</v>
       </c>
       <c r="E96">
-        <v>52.15986048982452</v>
+        <v>53.23321707485377</v>
       </c>
       <c r="F96">
-        <v>100.8955189927491</v>
+        <v>101.9688755777783</v>
       </c>
       <c r="G96">
         <v>4.91</v>
@@ -9400,37 +9400,37 @@
         <v>10.61</v>
       </c>
       <c r="M96">
-        <v>20.25982021374402</v>
+        <v>20.47535021601789</v>
       </c>
       <c r="N96">
-        <v>-9.649820213744016</v>
+        <v>-9.865350216017889</v>
       </c>
       <c r="O96">
-        <v>-2.122960447023684</v>
+        <v>-2.170377047523936</v>
       </c>
       <c r="P96">
-        <v>-7.526859766720333</v>
+        <v>-7.694973168493954</v>
       </c>
       <c r="Q96">
-        <v>-2.016859766720333</v>
+        <v>-2.184973168493954</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8013164257722565</v>
+        <v>0.9524197109267085</v>
       </c>
       <c r="T96">
-        <v>17.44841629959022</v>
+        <v>20.93809955950828</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1152132632656092</v>
+        <v>0.1140004920733396</v>
       </c>
       <c r="W96">
-        <v>0.1776651767362657</v>
+        <v>0.1779087011916734</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5236966512073145</v>
+        <v>0.5181840548788165</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9446,22 +9446,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2166342516784251</v>
+        <v>0.2181842516784251</v>
       </c>
       <c r="C97">
-        <v>-61.76857753600379</v>
+        <v>-63.12554624293081</v>
       </c>
       <c r="D97">
-        <v>35.29029804177454</v>
+        <v>35.00668591987677</v>
       </c>
       <c r="E97">
-        <v>53.23321707485377</v>
+        <v>54.30657365988301</v>
       </c>
       <c r="F97">
-        <v>101.9688755777783</v>
+        <v>103.0422321628076</v>
       </c>
       <c r="G97">
         <v>4.91</v>
@@ -9482,37 +9482,37 @@
         <v>10.61</v>
       </c>
       <c r="M97">
-        <v>20.47535021601789</v>
+        <v>20.69088021829176</v>
       </c>
       <c r="N97">
-        <v>-9.865350216017889</v>
+        <v>-10.08088021829176</v>
       </c>
       <c r="O97">
-        <v>-2.170377047523936</v>
+        <v>-2.217793648024188</v>
       </c>
       <c r="P97">
-        <v>-7.694973168493954</v>
+        <v>-7.863086570267575</v>
       </c>
       <c r="Q97">
-        <v>-2.184973168493954</v>
+        <v>-2.353086570267575</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9524197109267085</v>
+        <v>1.179074638658386</v>
       </c>
       <c r="T97">
-        <v>20.93809955950828</v>
+        <v>26.17262444938536</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1140004920733396</v>
+        <v>0.1128129869475757</v>
       </c>
       <c r="W97">
-        <v>0.1779087011916734</v>
+        <v>0.1781471522209268</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5181840548788165</v>
+        <v>0.5127863043071621</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9528,22 +9528,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2181842516784251</v>
+        <v>0.2197342516784251</v>
       </c>
       <c r="C98">
-        <v>-63.1255462429308</v>
+        <v>-64.47799276855599</v>
       </c>
       <c r="D98">
-        <v>35.00668591987679</v>
+        <v>34.72759597928083</v>
       </c>
       <c r="E98">
-        <v>54.30657365988301</v>
+        <v>55.37993024491226</v>
       </c>
       <c r="F98">
-        <v>103.0422321628076</v>
+        <v>104.1155887478368</v>
       </c>
       <c r="G98">
         <v>4.91</v>
@@ -9564,37 +9564,37 @@
         <v>10.61</v>
       </c>
       <c r="M98">
-        <v>20.69088021829176</v>
+        <v>20.90641022056564</v>
       </c>
       <c r="N98">
-        <v>-10.08088021829176</v>
+        <v>-10.29641022056563</v>
       </c>
       <c r="O98">
-        <v>-2.217793648024188</v>
+        <v>-2.26521024852444</v>
       </c>
       <c r="P98">
-        <v>-7.863086570267575</v>
+        <v>-8.031199972041195</v>
       </c>
       <c r="Q98">
-        <v>-2.353086570267575</v>
+        <v>-2.521199972041195</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.179074638658383</v>
+        <v>1.556832851544511</v>
       </c>
       <c r="T98">
-        <v>26.17262444938529</v>
+        <v>34.89683259918039</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1128129869475757</v>
+        <v>0.1116499664635801</v>
       </c>
       <c r="W98">
-        <v>0.1781471522209268</v>
+        <v>0.1783806867341131</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5127863043071621</v>
+        <v>0.5074998475617274</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9610,22 +9610,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2197342516784251</v>
+        <v>0.2212842516784251</v>
       </c>
       <c r="C99">
-        <v>-64.47799276855599</v>
+        <v>-65.82602441634202</v>
       </c>
       <c r="D99">
-        <v>34.72759597928083</v>
+        <v>34.45292091652404</v>
       </c>
       <c r="E99">
-        <v>55.37993024491226</v>
+        <v>56.4532868299415</v>
       </c>
       <c r="F99">
-        <v>104.1155887478368</v>
+        <v>105.1889453328661</v>
       </c>
       <c r="G99">
         <v>4.91</v>
@@ -9646,37 +9646,37 @@
         <v>10.61</v>
       </c>
       <c r="M99">
-        <v>20.90641022056564</v>
+        <v>21.12194022283951</v>
       </c>
       <c r="N99">
-        <v>-10.29641022056563</v>
+        <v>-10.51194022283951</v>
       </c>
       <c r="O99">
-        <v>-2.26521024852444</v>
+        <v>-2.312626849024692</v>
       </c>
       <c r="P99">
-        <v>-8.031199972041195</v>
+        <v>-8.199313373814816</v>
       </c>
       <c r="Q99">
-        <v>-2.521199972041195</v>
+        <v>-2.689313373814816</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.556832851544511</v>
+        <v>2.312349277316766</v>
       </c>
       <c r="T99">
-        <v>34.89683259918039</v>
+        <v>52.34524889877058</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1116499664635801</v>
+        <v>0.1105106810915027</v>
       </c>
       <c r="W99">
-        <v>0.1783806867341131</v>
+        <v>0.1786094552368263</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5074998475617274</v>
+        <v>0.5023212776886485</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9692,22 +9692,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2212842516784251</v>
+        <v>0.2583014570206978</v>
       </c>
       <c r="C100">
-        <v>-65.82602441634202</v>
+        <v>-72.37331589276522</v>
       </c>
       <c r="D100">
-        <v>34.45292091652404</v>
+        <v>28.97898602513009</v>
       </c>
       <c r="E100">
-        <v>56.4532868299415</v>
+        <v>57.52664341497075</v>
       </c>
       <c r="F100">
-        <v>105.1889453328661</v>
+        <v>106.2623019178953</v>
       </c>
       <c r="G100">
         <v>4.91</v>
@@ -9728,129 +9728,47 @@
         <v>10.61</v>
       </c>
       <c r="M100">
-        <v>21.12194022283951</v>
+        <v>25.05665079223972</v>
       </c>
       <c r="N100">
-        <v>-10.51194022283951</v>
+        <v>-14.44665079223971</v>
       </c>
       <c r="O100">
-        <v>-2.312626849024692</v>
+        <v>-3.178263174292737</v>
       </c>
       <c r="P100">
-        <v>-8.199313373814816</v>
+        <v>-11.26838761794698</v>
       </c>
       <c r="Q100">
-        <v>-2.689313373814816</v>
+        <v>-5.758387617946978</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.312349277316766</v>
+        <v>4.660619088860799</v>
       </c>
       <c r="T100">
-        <v>52.34524889877058</v>
+        <v>106.5778080568314</v>
       </c>
       <c r="U100">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1105106810915027</v>
+        <v>0.09315690350455474</v>
       </c>
       <c r="W100">
-        <v>0.1786094552368263</v>
+        <v>0.213833602153626</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.5023212776886485</v>
+        <v>0.4234404704752488</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2583014570206978</v>
-      </c>
-      <c r="C101">
-        <v>-72.37331589276522</v>
-      </c>
-      <c r="D101">
-        <v>28.97898602513009</v>
-      </c>
-      <c r="E101">
-        <v>57.52664341497075</v>
-      </c>
-      <c r="F101">
-        <v>106.2623019178953</v>
-      </c>
-      <c r="G101">
-        <v>4.91</v>
-      </c>
-      <c r="H101">
-        <v>58.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>16.12</v>
-      </c>
-      <c r="K101">
-        <v>5.51</v>
-      </c>
-      <c r="L101">
-        <v>10.61</v>
-      </c>
-      <c r="M101">
-        <v>25.05665079223972</v>
-      </c>
-      <c r="N101">
-        <v>-14.44665079223971</v>
-      </c>
-      <c r="O101">
-        <v>-3.178263174292737</v>
-      </c>
-      <c r="P101">
-        <v>-11.26838761794698</v>
-      </c>
-      <c r="Q101">
-        <v>-5.758387617946978</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.660619088860799</v>
-      </c>
-      <c r="T101">
-        <v>106.5778080568314</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09315690350455474</v>
-      </c>
-      <c r="W101">
-        <v>0.213833602153626</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4234404704752488</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
